--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y497"/>
+  <dimension ref="A1:Y522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,29 +617,33 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: hmongers Tas,...,.â€¦.</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+52A0 CJK UNIFIED IDEOGRAPH-52A0 | isolated marker/symbol line :: 加</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1,78 To Balance on hand from last year $ 48 14 cultivation. The lot extends to the Bay below â€”â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L15: symbol-only separator/garbage line :: 422.46</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+52A0 CJK UNIFIED IDEOGRAPH-52A0 | isolated marker/symbol line :: 加</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: hmongers Tas,...,.â€¦.</t>
+          <t>L19: punctuation artifact: repeated periods :: hmongers Tas,...,.….</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
@@ -649,7 +653,7 @@
       </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | line starts with punctuation glued to text :: *â€¦</t>
+          <t>L430: line starts with lowercase prefix glued to capitalized word :: aNd After MONDAY, SEVENTH</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -697,7 +701,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>L992: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "Summons issued in this cause" vs "Sumn 3000cause" :: â€” Canada, to the Writ of Sumn</t>
+          <t>L992: localized OCR phrase divergence vs other OCR: "Summons issued in this cause" vs "Sumn 3000cause" :: — Canada, to the Writ of Sumn</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -712,19 +716,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: to Ludger Dupont â€¦ s</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+25B2 BLACK UP-POINTING TRIANGLE :: water) at the of ▲ L</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal € n the occa-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L17: symbol-only separator/garbage line :: ******</t>
+          <t>L15: symbol-only separator/garbage line :: 422.46</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -742,11 +746,7 @@
           <t>L50: punctuation artifact: repeated periods :: Receipts from all sources ........6375,09 the Shawinegan Falls ; on it is erected the Go- Public in general ferae miitenced business,</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>L430: line starts with lowercase prefix glued to capitalized word :: aNd After MONDAY, SEVENTH</t>
-        </is>
-      </c>
+      <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
           <t>L134: line starts with punctuation glued to text :: *NIGHT EXPRESS,(with Sleeping</t>
@@ -802,24 +802,24 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L63: suspicious token(s): 1as (letter/digit mix) :: —1as will defy competition.</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Toe. Equire's barn,â€¦</t>
+          <t>L75: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Ladder ， Co</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L539: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 19. •. ** 200 sion; and the opportunity thus afforded to</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L18: symbol-only separator/garbage line :: 14207</t>
+          <t>L17: symbol-only separator/garbage line :: ******</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L55: punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He —1-----------" —he — in will</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -866,12 +866,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>648</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -894,19 +894,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L120: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L20: symbol-only separator/garbage line :: 3.10</t>
+          <t>L18: symbol-only separator/garbage line :: 14207</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L71: punctuation artifact: repeated periods :: Antoine Délorier 2 toisestone.. - 12,00</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -981,19 +981,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to Aim Ã© Penneton, far a Poll in</t>
+          <t>L131: stray/suspicious non-ASCII glyph(s): U+5F97 CJK UNIFIED IDEOGRAPH-5F97 | isolated marker/symbol line :: 得</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ,â€”"Wholesale and Retail.</t>
+          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ±7, " " 200 on or before the 15th day of July, and all such</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line :: 38.00</t>
+          <t>L20: symbol-only separator/garbage line :: 3.10</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1068,19 +1068,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
+          <t>L132: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” 1 sincere thanks to his friends and the</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L24: symbol-only separator/garbage line :: 5.25</t>
+          <t>L22: symbol-only separator/garbage line :: 38.00</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To Augustin Godin work â€”: 11,35</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Apply •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L26: symbol-only separator/garbage line :: 512.0</t>
+          <t>L24: symbol-only separator/garbage line :: 5.25</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1242,19 +1242,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | line starts with punctuation glued to text :: *â€¦</t>
+          <t>L161: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: To O: Lanigan ， Eaq.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: .</t>
+          <t>L26: symbol-only separator/garbage line :: 512.0</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: .</t>
+          <t>L28: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Receipts from all sources ...â€¦. ...â€¦</t>
+          <t>L174: punctuation artifact: repeated periods :: Receipts from all sources ...…. ...…</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1412,19 +1412,19 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Receipts from all sources ...â€¦. ...â€¦</t>
+          <t>L181: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L881: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Cash principle; and by this means will be•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L30: symbol-only separator/garbage line :: 58, 66</t>
+          <t>L29: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>521</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1495,19 +1495,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L216: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ© Panneton, for a Poll in</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 5</t>
+          <t>L30: symbol-only separator/garbage line :: 58, 66</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1528,7 +1528,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1578,19 +1578,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
+          <t>L280: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA, U+66F4 CJK UNIFIED IDEOGRAPH-66F4 :: 自 更</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L1134: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ Olivier Pothier for the large</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L33: symbol-only separator/garbage line :: 383.25</t>
+          <t>L32: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       <c r="V13" s="1" t="inlineStr"/>
       <c r="W13" s="1" t="inlineStr">
         <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
+          <t>L1351: abbreviation/spacing may be garbled :: Arriving in Montreal at — 6.30 P.M.</t>
         </is>
       </c>
       <c r="X13" s="1" t="inlineStr"/>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1661,19 +1661,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: è‡ª æ›´</t>
+          <t>L281: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Jesuitsâ€™ Estates &amp; Crown Domain Branch,</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L35: symbol-only separator/garbage line :: 11.00</t>
+          <t>L33: symbol-only separator/garbage line :: 383.25</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1694,7 +1694,7 @@
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1744,19 +1744,19 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è�‰</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 200 â€”</t>
+          <t>L1509: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L37: symbol-only separator/garbage line :: 7.00</t>
+          <t>L35: symbol-only separator/garbage line :: 11.00</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1777,7 +1777,7 @@
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
+          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
       <c r="E16" s="1" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>L1510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | suspicious token(s): TowiNG (odd internal casing) | candidate OCR token mismatch vs other OCR: "Dleep" vs "Deep" :: n â€¦(TowiNG on Dleep River, des-Chatts,</t>
+          <t>L1510: suspicious token(s): TowiNG (odd internal casing) | candidate OCR token mismatch vs other OCR: "Dleep" vs "Deep" :: n …(TowiNG on Dleep River, des-Chatts,</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr"/>
@@ -1827,19 +1827,19 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L284: stray/suspicious non-ASCII glyph(s): U+8349 CJK UNIFIED IDEOGRAPH-8349 | isolated marker/symbol line :: 草</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rue. Esquireâ€™s barn, .</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L39: symbol-only separator/garbage line :: 42.97</t>
+          <t>L37: symbol-only separator/garbage line :: 7.00</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1024: line starts with punctuation glued to text :: ** Rivière du Loup, at</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr"/>
@@ -1906,19 +1906,15 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I Quarter,.;.â€”</t>
-        </is>
-      </c>
+          <t>L314: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L41: symbol-only separator/garbage line :: 528, 00</t>
+          <t>L39: symbol-only separator/garbage line :: 42.97</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1939,7 +1935,7 @@
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="1" t="inlineStr">
         <is>
-          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr"/>
@@ -1973,19 +1969,15 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L327: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from Montreal on articles for Exhibitionâ€”</t>
-        </is>
-      </c>
+          <t>L322: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L43: symbol-only separator/garbage line :: 3.50</t>
+          <t>L41: symbol-only separator/garbage line :: 528, 00</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -2006,7 +1998,7 @@
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="T18" s="1" t="inlineStr"/>
@@ -2040,19 +2032,15 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER :: 6 ç¦�</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L416: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: approved by the Local Committeesâ€”will be</t>
-        </is>
-      </c>
+          <t>L340: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F :: 6 福</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L45: symbol-only separator/garbage line :: 60, 00</t>
+          <t>L43: symbol-only separator/garbage line :: 3.50</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -2073,7 +2061,7 @@
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
+          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr"/>
@@ -2103,19 +2091,15 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: ç”¨</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To G. Lanigan, Esq., .â€” 84.30</t>
-        </is>
-      </c>
+          <t>L379: stray/suspicious non-ASCII glyph(s): U+7528 CJK UNIFIED IDEOGRAPH-7528 | isolated marker/symbol line :: 用</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L48: symbol-only separator/garbage line :: 892, 00</t>
+          <t>L45: symbol-only separator/garbage line :: 60, 00</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -2136,7 +2120,7 @@
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr"/>
@@ -2156,7 +2140,7 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): atYamachiche27th (letter/digit mix) :: â€œYamachie,atYamachiche27th &amp; &amp;</t>
+          <t>L843: suspicious token(s): atYamachiche27th (letter/digit mix) :: “Yamachie,atYamachiche27th &amp; &amp;</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
@@ -2166,19 +2150,15 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L463: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€Š</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”|keeping, to examine, compare and stamp all</t>
-        </is>
-      </c>
+          <t>L462: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L51: symbol-only separator/garbage line :: 1906.30</t>
+          <t>L48: symbol-only separator/garbage line :: 892, 00</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -2188,7 +2168,7 @@
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>L619: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Interest,...*â€¦</t>
+          <t>L619: punctuation artifact: repeated periods :: Interest,...*…</t>
         </is>
       </c>
       <c r="Q21" s="1" t="inlineStr">
@@ -2199,7 +2179,7 @@
       <c r="R21" s="1" t="inlineStr"/>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr"/>
@@ -2219,7 +2199,7 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>L906: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amachiche27th (letter/digit mix) :: amachiche27th &amp; 28th â€œ</t>
+          <t>L906: suspicious token(s): amachiche27th (letter/digit mix) :: amachiche27th &amp; 28th “</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
@@ -2229,19 +2209,15 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Becancour and Ste. Gertrude,</t>
-        </is>
-      </c>
+          <t>L477: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: $6375, 00</t>
+          <t>L51: symbol-only separator/garbage line :: 1906.30</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2256,13 +2232,13 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L172: punctuation artifact: repeated periods :: Salaries.........- — ......</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr"/>
@@ -2292,19 +2268,15 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L542: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Rivers Turf Club will be held at the Court.</t>
-        </is>
-      </c>
+          <t>L542: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 30</t>
+          <t>L52: symbol-only separator/garbage line :: $6375, 00</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2314,7 +2286,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: corporation,...,â€¦.****</t>
+          <t>L653: punctuation artifact: repeated periods :: corporation,...,….****</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
@@ -2323,7 +2295,11 @@
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+        </is>
+      </c>
       <c r="T23" s="1" t="inlineStr"/>
       <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" s="1" t="inlineStr"/>
@@ -2351,19 +2327,15 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: House on Monday next 9th inst, at 2 oâ€™clockI</t>
-        </is>
-      </c>
+          <t>L576: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: S</t>
+          <t>L55: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2382,7 +2354,11 @@
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
       <c r="T24" s="1" t="inlineStr"/>
       <c r="U24" s="1" t="inlineStr"/>
       <c r="V24" s="1" t="inlineStr"/>
@@ -2410,19 +2386,15 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal â‚¬ n the occa-</t>
-        </is>
-      </c>
+          <t>L593: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 70</t>
+          <t>L57: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2469,19 +2441,15 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L596: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Secretary Treasurer, â€¦.</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 19. â€¢. ** 200 sion; and the opportunity thus afforded to</t>
-        </is>
-      </c>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L64: symbol-only separator/garbage line :: 75.00</t>
+          <t>L60: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2523,24 +2491,20 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
+          <t>L1587: suspicious token(s): AyImer (odd internal casing) :: the U. F. Co’s: Office, AyImer, or on Board</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>L600: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Messenger,â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 98-â€¢ " 200 Establishments, will use every effort to make</t>
-        </is>
-      </c>
+          <t>L770: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L68: symbol-only separator/garbage line :: 18.6</t>
+          <t>L64: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2587,19 +2551,15 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>L619: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Interest,...*â€¦</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Â±7, " " 200 on or before the 15th day of July, and all such</t>
-        </is>
-      </c>
+          <t>L821: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | punctuation artifact: repeated periods :: " Batiscan ， at Batisean...</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L70: symbol-only separator/garbage line :: 1.00</t>
+          <t>L68: symbol-only separator/garbage line :: 18.6</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2642,19 +2602,15 @@
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
-        </is>
-      </c>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: 10.00</t>
+          <t>L70: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2664,7 +2620,7 @@
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>L821: punctuation artifact: repeated periods :: " Batiscan ï¼Œ at Batisean...</t>
+          <t>L821: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | punctuation artifact: repeated periods :: " Batiscan ， at Batisean...</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
@@ -2697,19 +2653,15 @@
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: corporation,...,â€¦.****</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L560: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SENGERSâ€”</t>
-        </is>
-      </c>
+          <t>L875: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 3</t>
+          <t>L78: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2724,7 +2676,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L193: punctuation artifact: repeated periods :: rehant’s Liquor Licence,.... 512,00</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2752,24 +2704,20 @@
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
-        </is>
-      </c>
+          <t>L922: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 800</t>
+          <t>L81: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L304: symbol-only separator/garbage line :: 20"</t>
+          <t>L302: symbol-only separator/garbage line :: 200 —</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2779,7 +2727,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L194: punctuation artifact: repeated periods :: as Â« Rentes,.............58,66</t>
+          <t>L194: punctuation artifact: repeated periods :: as « Rentes,.............58,66</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2807,24 +2755,20 @@
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Apply â€¢</t>
-        </is>
-      </c>
+          <t>L970: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 400</t>
+          <t>L82: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L316: symbol-only separator/garbage line :: 14.00</t>
+          <t>L304: symbol-only separator/garbage line :: 20"</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2862,24 +2806,20 @@
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œRadnor Forges, at Forges</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Montreal, 10 April. 1860 â€˜84</t>
-        </is>
-      </c>
+          <t>L971: stray/suspicious non-ASCII glyph(s): U+5668 CJK UNIFIED IDEOGRAPH-5668 | isolated marker/symbol line :: 器</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: 12.00</t>
+          <t>L84: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L318: symbol-only separator/garbage line :: 4-00</t>
+          <t>L316: symbol-only separator/garbage line :: 14.00</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2889,7 +2829,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L196: punctuation artifact: repeated periods :: dlar’s Licence,..........13,00</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2911,30 +2851,26 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>L1510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | suspicious token(s): TowiNG (odd internal casing) | candidate OCR token mismatch vs other OCR: "Dleep" vs "Deep" :: n â€¦(TowiNG on Dleep River, des-Chatts,</t>
+          <t>L1510: suspicious token(s): TowiNG (odd internal casing) | candidate OCR token mismatch vs other OCR: "Dleep" vs "Deep" :: n …(TowiNG on Dleep River, des-Chatts,</t>
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: viere du Loup. â€¦ â€¦. 18th &amp; 1</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
-        </is>
-      </c>
+          <t>L972: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L88: symbol-only separator/garbage line :: 5, 38</t>
+          <t>L86: symbol-only separator/garbage line :: 12.00</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L320: symbol-only separator/garbage line :: 4.00</t>
+          <t>L318: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -2972,29 +2908,25 @@
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): atYamachiche27th (letter/digit mix) :: â€œYamachie,atYamachiche27th &amp; &amp;</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 5â€™0</t>
-        </is>
-      </c>
+          <t>L973: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L90: symbol-only separator/garbage line :: 30, 00</t>
+          <t>L88: symbol-only separator/garbage line :: 5, 38</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L322: symbol-only separator/garbage line :: 4.00</t>
+          <t>L320: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>L902: punctuation artifact: repeated periods :: Â·... 21st &amp; 22nd "</t>
+          <t>L902: punctuation artifact: repeated periods :: ·... 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="Q35" s="1" t="inlineStr">
@@ -3027,24 +2959,20 @@
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: intituled,â€œan Act</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 13th â€”</t>
-        </is>
-      </c>
+          <t>L986: stray/suspicious non-ASCII glyph(s): U+9760 CJK UNIFIED IDEOGRAPH-9760 | isolated marker/symbol line :: 靠</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 5, 00</t>
+          <t>L90: symbol-only separator/garbage line :: 30, 00</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L324: symbol-only separator/garbage line :: 4.00</t>
+          <t>L322: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -3082,29 +3010,25 @@
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L778: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: 4 Grande RiviÃ¨re, at the Ferry</t>
-        </is>
-      </c>
+          <t>L988: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 1</t>
+          <t>L92: symbol-only separator/garbage line :: 5, 00</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L324: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>L1019: punctuation artifact: repeated periods :: ... 7 Î”. M.</t>
+          <t>L1019: punctuation artifact: repeated periods :: ... 7 Δ. M.</t>
         </is>
       </c>
       <c r="Q37" s="1" t="inlineStr">
@@ -3137,24 +3061,20 @@
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 75</t>
+          <t>L94: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L350: isolated marker/symbol line :: 30</t>
+          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3192,24 +3112,20 @@
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>L896: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 25th â€œ</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢ St. Stanislas and St. Tite,</t>
-        </is>
-      </c>
+          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: ± 5</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L98: symbol-only separator/garbage line :: 36, 60</t>
+          <t>L96: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L352: symbol-only separator/garbage line :: 31.00</t>
+          <t>L350: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3247,24 +3163,20 @@
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>L898: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 28th &amp; 29th â€œ</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
-        </is>
-      </c>
+          <t>L1056: stray/suspicious non-ASCII glyph(s): U+697C CJK UNIFIED IDEOGRAPH-697C | isolated marker/symbol line :: 楼</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L100: symbol-only separator/garbage line :: 26.70</t>
+          <t>L98: symbol-only separator/garbage line :: 36, 60</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
+          <t>L352: symbol-only separator/garbage line :: 31.00</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -3302,29 +3214,25 @@
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr">
         <is>
-          <t>L903: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Cash principle; and by this means will beâ€¢</t>
-        </is>
-      </c>
+          <t>L1089: stray/suspicious non-ASCII glyph(s): U+7ECF CJK UNIFIED IDEOGRAPH-7ECF, U+6E90 CJK UNIFIED IDEOGRAPH-6E90 :: 经 源</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 32</t>
+          <t>L100: symbol-only separator/garbage line :: 26.70</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
+          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
-          <t>L1193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: ComsionerÂ·Street...â€¦...</t>
+          <t>L1193: punctuation artifact: repeated periods :: Comsioner·Street...…...</t>
         </is>
       </c>
       <c r="Q41" s="1" t="inlineStr">
@@ -3353,24 +3261,20 @@
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>L906: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amachiche27th (letter/digit mix) :: amachiche27th &amp; 28th â€œ</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+          <t>L1109: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L105: symbol-only separator/garbage line :: 1, 78</t>
+          <t>L103: isolated marker/symbol line :: 32</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
+          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr">
@@ -3404,29 +3308,25 @@
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>L909: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 29th â€œ</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 30th â€œ</t>
-        </is>
-      </c>
+          <t>L1111: stray/suspicious non-ASCII glyph(s): U+4E8B CJK UNIFIED IDEOGRAPH-4E8B | isolated marker/symbol line :: 事</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 1</t>
+          <t>L105: symbol-only separator/garbage line :: 1, 78</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
+          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr">
         <is>
-          <t>L1217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: The Inspector ... ...â€¦</t>
+          <t>L1217: punctuation artifact: repeated periods :: The Inspector ... ...…</t>
         </is>
       </c>
       <c r="Q43" s="1" t="inlineStr">
@@ -3455,24 +3355,20 @@
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>L922: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4th â€œ</t>
-        </is>
-      </c>
+          <t>L1112: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 17, 20</t>
+          <t>L108: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L361: symbol-only separator/garbage line :: 491.62</t>
+          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -3506,24 +3402,20 @@
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>L970: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L947: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ing L E. Pacaudâ€™s insur</t>
-        </is>
-      </c>
+          <t>L1121: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L112: symbol-only separator/garbage line :: 5.00</t>
+          <t>L109: symbol-only separator/garbage line :: 17, 20</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 70</t>
+          <t>L361: symbol-only separator/garbage line :: 491.62</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -3557,24 +3449,20 @@
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>L971: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A8 DIAERESIS | isolated marker/symbol line :: å™¨</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Expert Taxâ€™s occasion of</t>
-        </is>
-      </c>
+          <t>L1145: stray/suspicious non-ASCII glyph(s): U+6559 CJK UNIFIED IDEOGRAPH-6559 | isolated marker/symbol line :: 教</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L114: symbol-only separator/garbage line :: 5, 00</t>
+          <t>L112: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L363: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -3608,24 +3496,20 @@
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
-        </is>
-      </c>
+          <t>L1230: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。。</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L116: symbol-only separator/garbage line :: 1135</t>
+          <t>L114: symbol-only separator/garbage line :: 5, 00</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.80</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr">
@@ -3635,7 +3519,7 @@
       </c>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L238: punctuation artifact: repeated periods :: St. Philip’s Ward, ......</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3659,24 +3543,20 @@
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>L986: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é�</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜or euregistration Doucetâ€™s</t>
-        </is>
-      </c>
+          <t>L1260: stray/suspicious non-ASCII glyph(s): U+552E CJK UNIFIED IDEOGRAPH-552E | isolated marker/symbol line :: 售</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L118: symbol-only separator/garbage line :: 1.50</t>
+          <t>L116: symbol-only separator/garbage line :: 1135</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: h</t>
+          <t>L387: symbol-only separator/garbage line :: 18.80</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -3710,24 +3590,20 @@
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>L1014: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SENGERS â€”</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L992: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | localized OCR phrase divergence vs other OCR: "Summons issued in this cause" vs "Sumn 3000cause" :: â€” Canada, to the Writ of Sumn</t>
-        </is>
-      </c>
+          <t>L1264: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: c −</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L118: symbol-only separator/garbage line :: 1.50</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L510: symbol-only separator/garbage line :: 10.00</t>
+          <t>L397: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr">
@@ -3761,24 +3637,20 @@
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Â± 5</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
-        </is>
-      </c>
+          <t>L1291: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: .</t>
+          <t>L120: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 800</t>
+          <t>L510: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr">
@@ -3812,24 +3684,20 @@
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>L1056: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: æ¥¼</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1019: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: a MaskinongÃ©, at MaskinongÃ©11th &amp;</t>
-        </is>
-      </c>
+          <t>L1294: stray/suspicious non-ASCII glyph(s): U+96C5 CJK UNIFIED IDEOGRAPH-96C5 | isolated marker/symbol line :: 雅</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 46.00</t>
+          <t>L123: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L514: symbol-only separator/garbage line :: 4.00</t>
+          <t>L512: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr">
@@ -3863,24 +3731,20 @@
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>L1089: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ç»� æº�</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
-        </is>
-      </c>
+          <t>L1301: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 25</t>
+          <t>L124: symbol-only separator/garbage line :: 46.00</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L514: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr">
@@ -3914,24 +3778,20 @@
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>L1107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5th â€œ</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 44 St. LÃ©on, and Hunterstown,</t>
-        </is>
-      </c>
+          <t>L1418: stray/suspicious non-ASCII glyph(s): U+4FDD CJK UNIFIED IDEOGRAPH-4FDD | isolated marker/symbol line :: 保</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L133: symbol-only separator/garbage line :: 1.00</t>
+          <t>L126: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L518: symbol-only separator/garbage line :: 91.30</t>
+          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -3965,24 +3825,20 @@
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>L1114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: askinong Ith &amp; 12th â€œ</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
-        </is>
-      </c>
+          <t>L1427: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L137: symbol-only separator/garbage line :: 14.00</t>
+          <t>L131: stray/suspicious non-ASCII glyph(s): U+5F97 CJK UNIFIED IDEOGRAPH-5F97 | isolated marker/symbol line :: 得</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L528: symbol-only separator/garbage line :: 480.00</t>
+          <t>L518: symbol-only separator/garbage line :: 91.30</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr">
@@ -4016,24 +3872,20 @@
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>L1127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15th â€œ</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1031: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " St. BarnabÃ© &amp; St. Paulin,</t>
-        </is>
-      </c>
+          <t>L1433: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L132: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L580: symbol-only separator/garbage line :: 8.00</t>
+          <t>L528: symbol-only separator/garbage line :: 480.00</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr">
@@ -4067,24 +3919,20 @@
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>L1145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+2122 TRADE MARK SIGN | isolated marker/symbol line :: æ•™</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
-        </is>
-      </c>
+          <t>L1525: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP :: RIVER. 。</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L141: symbol-only separator/garbage line :: 4-00</t>
+          <t>L133: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 5.00</t>
+          <t>L580: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr">
@@ -4118,24 +3966,20 @@
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>L1193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: ComsionerÂ·Street...â€¦...</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1046: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a St Etienne, at St Etienne 6th â€œ</t>
-        </is>
-      </c>
+          <t>L1569: stray/suspicious non-ASCII glyph(s): U+94F6 CJK UNIFIED IDEOGRAPH-94F6 | isolated marker/symbol line :: 银</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L143: symbol-only separator/garbage line :: 4.00</t>
+          <t>L137: symbol-only separator/garbage line :: 14.00</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L584: symbol-only separator/garbage line :: 8.00</t>
+          <t>L582: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr">
@@ -4169,24 +4013,20 @@
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>L1217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: The Inspector ... ...â€¦</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Kiernanâ€™s Commercial Buildings,</t>
-        </is>
-      </c>
+          <t>L1577: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: follows: 一</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L145: symbol-only separator/garbage line :: 4.00</t>
+          <t>L140: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
+          <t>L584: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr">
@@ -4220,24 +4060,20 @@
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>L1230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚ã€‚</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+          <t>L1578: stray/suspicious non-ASCII glyph(s): U+9001 CJK UNIFIED IDEOGRAPH-9001 :: S 送</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L147: symbol-only separator/garbage line :: 4.00</t>
+          <t>L141: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L611: isolated marker/symbol line :: 9</t>
+          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr">
@@ -4271,24 +4107,20 @@
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr">
         <is>
-          <t>L1257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1228: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Any person or persons who neglects</t>
-        </is>
-      </c>
+          <t>L1580: stray/suspicious non-ASCII glyph(s): U+7EF4 CJK UNIFIED IDEOGRAPH-7EF4 | isolated marker/symbol line :: 维</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L149: symbol-only separator/garbage line :: 125.75</t>
+          <t>L143: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L613: symbol-only separator/garbage line :: 4 00</t>
+          <t>L611: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -4318,24 +4150,20 @@
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>L1260: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å”®</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1242: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ VIEWS ON THE</t>
-        </is>
-      </c>
+          <t>L1620: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: P: Prescription ， with full directions Cifre</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L145: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: 18</t>
+          <t>L613: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -4365,24 +4193,20 @@
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>L1317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: i da Louis Godin.â€¦</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” CAPT. CUMING, 7 F MRS. FRANCIS PATTI BAINS, who</t>
-        </is>
-      </c>
+          <t>L1628: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L153: symbol-only separator/garbage line :: 127.45</t>
+          <t>L147: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L616: symbol-only separator/garbage line :: 100.00</t>
+          <t>L614: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -4412,24 +4236,20 @@
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>L1324: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: steamer OREGON at Chattsâ€™ Railroad, and tary to General Platt in 1813. , GRECO</t>
-        </is>
-      </c>
+          <t>L1631: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 1</t>
+          <t>L149: symbol-only separator/garbage line :: 125.75</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 6.90</t>
+          <t>L616: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -4459,24 +4279,20 @@
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>L1332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” Brooklyn, Long Island, N. Y. who will be</t>
-        </is>
-      </c>
+          <t>L1637: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L156: symbol-only separator/garbage line :: 113.97</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L642: symbol-only separator/garbage line :: 24.00</t>
+          <t>L627: symbol-only separator/garbage line :: 6.90</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -4506,24 +4322,20 @@
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>L1418: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ä¿�</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
-        </is>
-      </c>
+          <t>L1638: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: 2 ，</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L158: symbol-only separator/garbage line :: 125 15</t>
+          <t>L153: symbol-only separator/garbage line :: 127.45</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: 50</t>
+          <t>L642: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -4551,26 +4363,18 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L1510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | suspicious token(s): TowiNG (odd internal casing) | candidate OCR token mismatch vs other OCR: "Dleep" vs "Deep" :: n â€¦(TowiNG on Dleep River, des-Chatts,</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L159: symbol-only separator/garbage line :: 491.62</t>
+          <t>L154: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L689: symbol-only separator/garbage line :: 4.05</t>
+          <t>L687: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4598,26 +4402,18 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L1525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: RIVER. ã€‚</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: I given to AimÃ© Panneton X ;</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L162: symbol-only separator/garbage line :: 84.30</t>
+          <t>L155: isolated marker/symbol line :: *…</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L710: symbol-only separator/garbage line :: 62.00</t>
+          <t>L689: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4645,26 +4441,18 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L1577: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: follows: ä¸€</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ruing at 1 â€˜Clock [Sundays excepted,]</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L156: symbol-only separator/garbage line :: 113.97</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: 15</t>
+          <t>L710: symbol-only separator/garbage line :: 62.00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4692,26 +4480,18 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L1578: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: S é€�</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Chattâ€™s Railroad, and returning thence to</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L168: isolated marker/symbol line :: 0</t>
+          <t>L158: symbol-only separator/garbage line :: 125 15</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L714: symbol-only separator/garbage line :: 9.50</t>
+          <t>L712: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4739,26 +4519,18 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L1580: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | isolated marker/symbol line :: ç»´</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1478: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜HE SUBSCRIBER respectfully informs</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L173: symbol-only separator/garbage line :: $48, 14</t>
+          <t>L159: symbol-only separator/garbage line :: 491.62</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L716: isolated marker/symbol line :: n</t>
+          <t>L714: symbol-only separator/garbage line :: 9.50</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4786,26 +4558,18 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L1628: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L175: symbol-only separator/garbage line :: 6375.09</t>
+          <t>L162: symbol-only separator/garbage line :: 84.30</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L728: symbol-only separator/garbage line :: 4 50</t>
+          <t>L716: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4833,26 +4597,18 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L1637: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HE Subscriber, for several years a restâ€”</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L177: symbol-only separator/garbage line :: $6856, 13</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L730: isolated marker/symbol line :: 37</t>
+          <t>L717: symbol-only separator/garbage line :: 5’0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4881,21 +4637,17 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: simple vegetable remedyâ€”a sure Cure for</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: 7</t>
+          <t>L168: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: 90</t>
+          <t>L728: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4924,21 +4676,17 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜othose who desire it, he will send the</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L173: symbol-only separator/garbage line :: $48, 14</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L749: isolated marker/symbol line :: A</t>
+          <t>L730: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4967,21 +4715,17 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L211: isolated marker/symbol line :: , 3</t>
+          <t>L175: symbol-only separator/garbage line :: 6375.09</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L751: symbol-only separator/garbage line :: 40.00</t>
+          <t>L732: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -5010,21 +4754,17 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and ** Anne Sisson,â€� either by the Hour, by</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L212: isolated marker/symbol line :: e</t>
+          <t>L177: symbol-only separator/garbage line :: $6856, 13</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line :: 1.00</t>
+          <t>L749: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -5053,21 +4793,17 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L213: isolated marker/symbol line :: 0</t>
+          <t>L180: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L762: isolated marker/symbol line :: 70</t>
+          <t>L751: symbol-only separator/garbage line :: 40.00</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -5096,27 +4832,23 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L215: isolated marker/symbol line :: 4</t>
+          <t>L181: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L764: symbol-only separator/garbage line :: 16 00</t>
+          <t>L760: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
       <c r="Q78" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="R78" s="1" t="inlineStr"/>
@@ -5139,27 +4871,23 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1612: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
+          <t>L211: isolated marker/symbol line :: , 3</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L766: symbol-only separator/garbage line :: 32.00</t>
+          <t>L762: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr"/>
@@ -5182,27 +4910,23 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L218: isolated marker/symbol line :: 0</t>
+          <t>L212: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L787: isolated marker/symbol line :: n</t>
+          <t>L764: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
+          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
         </is>
       </c>
       <c r="R80" s="1" t="inlineStr"/>
@@ -5225,27 +4949,23 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Natureâ€™s simple herbs. Those desiring the</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L221: symbol-only separator/garbage line :: 6-0</t>
+          <t>L213: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L798: symbol-only separator/garbage line :: 50.00</t>
+          <t>L766: symbol-only separator/garbage line :: 32.00</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
       <c r="Q81" s="1" t="inlineStr">
         <is>
-          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
+          <t>L564: punctuation artifact: repeated periods :: Arriving in Montreal,.........—7 A. M.</t>
         </is>
       </c>
       <c r="R81" s="1" t="inlineStr"/>
@@ -5273,18 +4993,18 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L226: isolated marker/symbol line :: 4</t>
+          <t>L215: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L800: symbol-only separator/garbage line :: 3 37</t>
+          <t>L787: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr">
         <is>
-          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
+          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
         </is>
       </c>
       <c r="R82" s="1" t="inlineStr"/>
@@ -5312,18 +5032,18 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L243: isolated marker/symbol line :: '</t>
+          <t>L216: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L802: isolated marker/symbol line :: 36</t>
+          <t>L798: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr">
         <is>
-          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
+          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
         </is>
       </c>
       <c r="R83" s="1" t="inlineStr"/>
@@ -5351,18 +5071,18 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L246: symbol-only separator/garbage line :: 334.31</t>
+          <t>L218: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L800: symbol-only separator/garbage line :: 3 37</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
+          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
         </is>
       </c>
       <c r="R84" s="1" t="inlineStr"/>
@@ -5390,18 +5110,18 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L249: symbol-only separator/garbage line :: 116.37</t>
+          <t>L221: symbol-only separator/garbage line :: 6-0</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L827: symbol-only separator/garbage line :: 1.25</t>
+          <t>L802: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
+          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
         </is>
       </c>
       <c r="R85" s="1" t="inlineStr"/>
@@ -5429,18 +5149,18 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L252: symbol-only separator/garbage line :: 523, 45</t>
+          <t>L226: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L829: symbol-only separator/garbage line :: 7.25</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
       <c r="Q86" s="1" t="inlineStr">
         <is>
-          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
+          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
         </is>
       </c>
       <c r="R86" s="1" t="inlineStr"/>
@@ -5468,18 +5188,18 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L254: symbol-only separator/garbage line :: 86.30</t>
+          <t>L243: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L832: symbol-only separator/garbage line :: 2.00</t>
+          <t>L827: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
       <c r="Q87" s="1" t="inlineStr">
         <is>
-          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
+          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
         </is>
       </c>
       <c r="R87" s="1" t="inlineStr"/>
@@ -5507,18 +5227,18 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L256: symbol-only separator/garbage line :: 127.33</t>
+          <t>L246: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>L854: symbol-only separator/garbage line :: 5,21</t>
+          <t>L829: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr">
         <is>
-          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
+          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
         </is>
       </c>
       <c r="R88" s="1" t="inlineStr"/>
@@ -5546,18 +5266,18 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L258: symbol-only separator/garbage line :: 3.0</t>
+          <t>L249: symbol-only separator/garbage line :: 116.37</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>L856: symbol-only separator/garbage line :: 1.30</t>
+          <t>L832: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr">
         <is>
-          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
+          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
         </is>
       </c>
       <c r="R89" s="1" t="inlineStr"/>
@@ -5585,18 +5305,18 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L260: symbol-only separator/garbage line :: 491, 62</t>
+          <t>L252: symbol-only separator/garbage line :: 523, 45</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>L858: symbol-only separator/garbage line :: 21 00</t>
+          <t>L854: symbol-only separator/garbage line :: 5,21</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
+          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
         </is>
       </c>
       <c r="R90" s="1" t="inlineStr"/>
@@ -5624,18 +5344,18 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L262: symbol-only separator/garbage line :: 91.00</t>
+          <t>L254: symbol-only separator/garbage line :: 86.30</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L856: symbol-only separator/garbage line :: 1.30</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
+          <t>L673: punctuation artifact: repeated periods :: at station No. I, —..</t>
         </is>
       </c>
       <c r="R91" s="1" t="inlineStr"/>
@@ -5663,18 +5383,18 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L264: symbol-only separator/garbage line :: 48600</t>
+          <t>L256: symbol-only separator/garbage line :: 127.33</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>L913: isolated marker/symbol line :: C</t>
+          <t>L858: symbol-only separator/garbage line :: 21 00</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
+          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
         </is>
       </c>
       <c r="R92" s="1" t="inlineStr"/>
@@ -5702,18 +5422,18 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L266: symbol-only separator/garbage line :: 2621, 15</t>
+          <t>L258: symbol-only separator/garbage line :: 3.0</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
+          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
         </is>
       </c>
       <c r="R93" s="1" t="inlineStr"/>
@@ -5741,18 +5461,18 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L268: symbol-only separator/garbage line :: 526, 41</t>
+          <t>L260: symbol-only separator/garbage line :: 491, 62</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>L916: symbol-only separator/garbage line :: 16 00</t>
+          <t>L913: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
+          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
         </is>
       </c>
       <c r="R94" s="1" t="inlineStr"/>
@@ -5780,18 +5500,18 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L270: symbol-only separator/garbage line :: 427, 271</t>
+          <t>L262: symbol-only separator/garbage line :: 91.00</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>L918: symbol-only separator/garbage line :: 1.35</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
+          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
         </is>
       </c>
       <c r="R95" s="1" t="inlineStr"/>
@@ -5819,18 +5539,18 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L272: symbol-only separator/garbage line :: 523, 45</t>
+          <t>L264: symbol-only separator/garbage line :: 48600</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 00</t>
+          <t>L916: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
+          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
         </is>
       </c>
       <c r="R96" s="1" t="inlineStr"/>
@@ -5858,18 +5578,18 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L273: symbol-only separator/garbage line :: $6856, 23</t>
+          <t>L266: symbol-only separator/garbage line :: 2621, 15</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: C.</t>
+          <t>L918: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
+          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
         </is>
       </c>
       <c r="R97" s="1" t="inlineStr"/>
@@ -5897,18 +5617,18 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: ,</t>
+          <t>L268: symbol-only separator/garbage line :: 526, 41</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>L998: isolated marker/symbol line :: C</t>
+          <t>L920: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr"/>
       <c r="Q98" s="1" t="inlineStr">
         <is>
-          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
+          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
         </is>
       </c>
       <c r="R98" s="1" t="inlineStr"/>
@@ -5936,18 +5656,18 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L276: isolated marker/symbol line :: 2</t>
+          <t>L270: symbol-only separator/garbage line :: 427, 271</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
+          <t>L921: isolated marker/symbol line :: C.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr"/>
       <c r="Q99" s="1" t="inlineStr">
         <is>
-          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
+          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R99" s="1" t="inlineStr"/>
@@ -5975,18 +5695,18 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L277: isolated marker/symbol line :: 2</t>
+          <t>L272: symbol-only separator/garbage line :: 523, 45</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 66</t>
+          <t>L998: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr"/>
       <c r="Q100" s="1" t="inlineStr">
         <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
+          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
         </is>
       </c>
       <c r="R100" s="1" t="inlineStr"/>
@@ -6014,18 +5734,18 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L278: symbol-only separator/garbage line :: 86.30</t>
+          <t>L273: symbol-only separator/garbage line :: $6856, 23</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: 1"</t>
+          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr"/>
       <c r="Q101" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L873: punctuation artifact: repeated periods :: — at St. Stanislas.........28th &amp; 29th "</t>
         </is>
       </c>
       <c r="R101" s="1" t="inlineStr"/>
@@ -6053,18 +5773,18 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L279: symbol-only separator/garbage line :: 197.331</t>
+          <t>L275: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1052: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="R102" s="1" t="inlineStr"/>
@@ -6092,18 +5812,18 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L281: isolated marker/symbol line :: â†’</t>
+          <t>L276: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1054: isolated marker/symbol line :: 1"</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="R103" s="1" t="inlineStr"/>
@@ -6131,18 +5851,18 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L283: symbol-only separator/garbage line :: 31.00</t>
+          <t>L277: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr">
         <is>
-          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
+          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
+          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr"/>
@@ -6170,18 +5890,18 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è�‰</t>
+          <t>L278: symbol-only separator/garbage line :: 86.30</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr">
         <is>
-          <t>L1094: isolated marker/symbol line :: 39</t>
+          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
+          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
         </is>
       </c>
       <c r="R105" s="1" t="inlineStr"/>
@@ -6209,18 +5929,18 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L285: isolated marker/symbol line :: 3</t>
+          <t>L279: symbol-only separator/garbage line :: 197.331</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr">
         <is>
-          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
+          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
         </is>
       </c>
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
+          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
         </is>
       </c>
       <c r="R106" s="1" t="inlineStr"/>
@@ -6248,18 +5968,18 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: o</t>
+          <t>L281: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr">
         <is>
-          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
+          <t>L1094: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
+          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
         </is>
       </c>
       <c r="R107" s="1" t="inlineStr"/>
@@ -6287,18 +6007,18 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr">
         <is>
-          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
+          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
+          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
         </is>
       </c>
       <c r="R108" s="1" t="inlineStr"/>
@@ -6326,18 +6046,18 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L317: isolated marker/symbol line :: 93</t>
+          <t>L283: symbol-only separator/garbage line :: 31.00</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr">
         <is>
-          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
+          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
         </is>
       </c>
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
+          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
         </is>
       </c>
       <c r="R109" s="1" t="inlineStr"/>
@@ -6365,18 +6085,18 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å­�</t>
+          <t>L284: stray/suspicious non-ASCII glyph(s): U+8349 CJK UNIFIED IDEOGRAPH-8349 | isolated marker/symbol line :: 草</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
         </is>
       </c>
       <c r="P110" s="1" t="inlineStr"/>
       <c r="Q110" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
+          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
         </is>
       </c>
       <c r="R110" s="1" t="inlineStr"/>
@@ -6404,18 +6124,18 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L324: symbol-only separator/garbage line :: 24,</t>
+          <t>L285: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr">
         <is>
-          <t>L1136: isolated marker/symbol line :: a-</t>
+          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P111" s="1" t="inlineStr"/>
       <c r="Q111" s="1" t="inlineStr">
         <is>
-          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
+          <t>L966: punctuation artifact: repeated periods :: the Governor’s visit,....</t>
         </is>
       </c>
       <c r="R111" s="1" t="inlineStr"/>
@@ -6443,18 +6163,18 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L325: isolated marker/symbol line :: 6</t>
+          <t>L298: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr">
         <is>
-          <t>L1138: isolated marker/symbol line :: 77</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="P112" s="1" t="inlineStr"/>
       <c r="Q112" s="1" t="inlineStr">
         <is>
-          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
+          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
         </is>
       </c>
       <c r="R112" s="1" t="inlineStr"/>
@@ -6482,18 +6202,18 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: "</t>
+          <t>L314: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr">
         <is>
-          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
+          <t>L1136: isolated marker/symbol line :: a-</t>
         </is>
       </c>
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
+          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
         </is>
       </c>
       <c r="R113" s="1" t="inlineStr"/>
@@ -6521,18 +6241,18 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L328: isolated marker/symbol line :: 39</t>
+          <t>L317: isolated marker/symbol line :: 93</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr">
         <is>
-          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
+          <t>L1138: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P114" s="1" t="inlineStr"/>
       <c r="Q114" s="1" t="inlineStr">
         <is>
-          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
+          <t>L1007: punctuation artifact: repeated periods :: strong’s fire, —........</t>
         </is>
       </c>
       <c r="R114" s="1" t="inlineStr"/>
@@ -6560,18 +6280,18 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L330: isolated marker/symbol line :: 68</t>
+          <t>L322: stray/suspicious non-ASCII glyph(s): U+5B50 CJK UNIFIED IDEOGRAPH-5B50 | isolated marker/symbol line :: 子</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr">
         <is>
-          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
+          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
         </is>
       </c>
       <c r="P115" s="1" t="inlineStr"/>
       <c r="Q115" s="1" t="inlineStr">
         <is>
-          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
+          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
         </is>
       </c>
       <c r="R115" s="1" t="inlineStr"/>
@@ -6599,18 +6319,18 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L331: isolated marker/symbol line :: 48</t>
+          <t>L324: symbol-only separator/garbage line :: 24,</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr">
         <is>
-          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
+          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
         </is>
       </c>
       <c r="P116" s="1" t="inlineStr"/>
       <c r="Q116" s="1" t="inlineStr">
         <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
+          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
         </is>
       </c>
       <c r="R116" s="1" t="inlineStr"/>
@@ -6638,18 +6358,18 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L332: isolated marker/symbol line :: 200</t>
+          <t>L325: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr">
         <is>
-          <t>L1190: isolated marker/symbol line :: -</t>
+          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
         </is>
       </c>
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
+          <t>L1029: punctuation artifact: repeated periods :: at St. Léon................ 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R117" s="1" t="inlineStr"/>
@@ -6677,18 +6397,18 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: 4</t>
+          <t>L326: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr">
         <is>
-          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
+          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
         </is>
       </c>
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
+          <t>L1032: punctuation artifact: repeated periods :: at St. Barnabé............25th &amp; 26th "</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr"/>
@@ -6716,18 +6436,18 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L335: isolated marker/symbol line :: "</t>
+          <t>L327: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr">
         <is>
-          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
+          <t>L1190: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P119" s="1" t="inlineStr"/>
       <c r="Q119" s="1" t="inlineStr">
         <is>
-          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
+          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
         </is>
       </c>
       <c r="R119" s="1" t="inlineStr"/>
@@ -6755,18 +6475,18 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: 200</t>
+          <t>L328: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr">
         <is>
-          <t>L1197: isolated marker/symbol line :: 5</t>
+          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
+          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
         </is>
       </c>
       <c r="R120" s="1" t="inlineStr"/>
@@ -6794,18 +6514,18 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L337: symbol-only separator/garbage line :: 26,</t>
+          <t>L330: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
         </is>
       </c>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
         </is>
       </c>
       <c r="R121" s="1" t="inlineStr"/>
@@ -6833,18 +6553,18 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L338: isolated marker/symbol line :: " 6</t>
+          <t>L331: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr">
         <is>
-          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
+          <t>L1197: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P122" s="1" t="inlineStr"/>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="R122" s="1" t="inlineStr"/>
@@ -6872,18 +6592,18 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L339: isolated marker/symbol line :: 66</t>
+          <t>L332: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr">
         <is>
-          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="P123" s="1" t="inlineStr"/>
       <c r="Q123" s="1" t="inlineStr">
         <is>
-          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
+          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
         </is>
       </c>
       <c r="R123" s="1" t="inlineStr"/>
@@ -6911,18 +6631,18 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: 68</t>
+          <t>L334: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr">
         <is>
-          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
+          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="P124" s="1" t="inlineStr"/>
       <c r="Q124" s="1" t="inlineStr">
         <is>
-          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
+          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
         </is>
       </c>
       <c r="R124" s="1" t="inlineStr"/>
@@ -6950,18 +6670,18 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L342: isolated marker/symbol line :: 210</t>
+          <t>L335: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr">
         <is>
-          <t>L1224: isolated marker/symbol line :: 240</t>
+          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
         </is>
       </c>
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr"/>
@@ -6989,18 +6709,18 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L344: isolated marker/symbol line :: 44</t>
+          <t>L336: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr">
         <is>
-          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
+          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
         </is>
       </c>
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr"/>
@@ -7028,18 +6748,18 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: 200</t>
+          <t>L337: symbol-only separator/garbage line :: 26,</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr">
         <is>
-          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
+          <t>L1224: isolated marker/symbol line :: 240</t>
         </is>
       </c>
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
+          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr"/>
@@ -7067,18 +6787,18 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L346: isolated marker/symbol line :: 24</t>
+          <t>L338: isolated marker/symbol line :: " 6</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr">
         <is>
-          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
+          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P128" s="1" t="inlineStr"/>
       <c r="Q128" s="1" t="inlineStr">
         <is>
-          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
+          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
         </is>
       </c>
       <c r="R128" s="1" t="inlineStr"/>
@@ -7106,18 +6826,18 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L347: isolated marker/symbol line :: 4</t>
+          <t>L339: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr">
         <is>
-          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
+          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
         </is>
       </c>
       <c r="P129" s="1" t="inlineStr"/>
       <c r="Q129" s="1" t="inlineStr">
         <is>
-          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
+          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
         </is>
       </c>
       <c r="R129" s="1" t="inlineStr"/>
@@ -7145,18 +6865,18 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L348: isolated marker/symbol line :: 6</t>
+          <t>L341: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr">
         <is>
-          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
+          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
         </is>
       </c>
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
+          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
         </is>
       </c>
       <c r="R130" s="1" t="inlineStr"/>
@@ -7184,18 +6904,18 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L349: isolated marker/symbol line :: 260</t>
+          <t>L342: isolated marker/symbol line :: 210</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr">
         <is>
-          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
         </is>
       </c>
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
+          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr"/>
@@ -7223,18 +6943,18 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L350: isolated marker/symbol line :: w</t>
+          <t>L344: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr">
         <is>
-          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
+          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
         </is>
       </c>
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
+          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr"/>
@@ -7262,18 +6982,18 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: "</t>
+          <t>L345: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr">
         <is>
-          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
+          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P133" s="1" t="inlineStr"/>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
+          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr"/>
@@ -7301,18 +7021,18 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L352: isolated marker/symbol line :: "</t>
+          <t>L346: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr">
         <is>
-          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
+          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
         </is>
       </c>
       <c r="P134" s="1" t="inlineStr"/>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
+          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
         </is>
       </c>
       <c r="R134" s="1" t="inlineStr"/>
@@ -7340,18 +7060,18 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: 200</t>
+          <t>L347: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
-          <t>L1274: symbol-only separator/garbage line :: 12]</t>
+          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
         </is>
       </c>
       <c r="P135" s="1" t="inlineStr"/>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr"/>
@@ -7379,18 +7099,18 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L354: isolated marker/symbol line :: 288</t>
+          <t>L348: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr">
         <is>
-          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
+          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
         </is>
       </c>
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr"/>
@@ -7418,18 +7138,18 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: 256</t>
+          <t>L349: isolated marker/symbol line :: 260</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr">
         <is>
-          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L1274: symbol-only separator/garbage line :: 12]</t>
         </is>
       </c>
       <c r="P137" s="1" t="inlineStr"/>
       <c r="Q137" s="1" t="inlineStr">
         <is>
-          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
+          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
         </is>
       </c>
       <c r="R137" s="1" t="inlineStr"/>
@@ -7457,18 +7177,18 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L356: isolated marker/symbol line :: . 8</t>
+          <t>L350: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr">
         <is>
-          <t>L1307: isolated marker/symbol line :: .</t>
+          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
         </is>
       </c>
       <c r="P138" s="1" t="inlineStr"/>
       <c r="Q138" s="1" t="inlineStr">
         <is>
-          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
+          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
         </is>
       </c>
       <c r="R138" s="1" t="inlineStr"/>
@@ -7496,18 +7216,18 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 64</t>
+          <t>L351: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: :s</t>
+          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="P139" s="1" t="inlineStr"/>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
+          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
         </is>
       </c>
       <c r="R139" s="1" t="inlineStr"/>
@@ -7535,18 +7255,18 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L358: isolated marker/symbol line :: 200</t>
+          <t>L352: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr">
         <is>
-          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
+          <t>L1307: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P140" s="1" t="inlineStr"/>
       <c r="Q140" s="1" t="inlineStr">
         <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
+          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
         </is>
       </c>
       <c r="R140" s="1" t="inlineStr"/>
@@ -7574,18 +7294,18 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: .</t>
+          <t>L353: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: 0</t>
+          <t>L1349: isolated marker/symbol line :: :s</t>
         </is>
       </c>
       <c r="P141" s="1" t="inlineStr"/>
       <c r="Q141" s="1" t="inlineStr">
         <is>
-          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
+          <t>L1420: punctuation artifact: repeated periods :: To Mr. Charles Dugré ........</t>
         </is>
       </c>
       <c r="R141" s="1" t="inlineStr"/>
@@ -7613,18 +7333,18 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L362: isolated marker/symbol line :: :</t>
+          <t>L354: isolated marker/symbol line :: 288</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P142" s="1" t="inlineStr"/>
       <c r="Q142" s="1" t="inlineStr">
         <is>
-          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
+          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
         </is>
       </c>
       <c r="R142" s="1" t="inlineStr"/>
@@ -7652,18 +7372,18 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 100</t>
+          <t>L355: isolated marker/symbol line :: 256</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1363: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
+          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr"/>
@@ -7691,18 +7411,18 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L364: isolated marker/symbol line :: 26</t>
+          <t>L356: isolated marker/symbol line :: . 8</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
+          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
         </is>
       </c>
       <c r="R144" s="1" t="inlineStr"/>
@@ -7730,18 +7450,18 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L365: isolated marker/symbol line :: 66</t>
+          <t>L357: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr">
         <is>
-          <t>L1490: isolated marker/symbol line :: 18</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="P145" s="1" t="inlineStr"/>
       <c r="Q145" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
         </is>
       </c>
       <c r="R145" s="1" t="inlineStr"/>
@@ -7769,18 +7489,18 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L367: isolated marker/symbol line :: 2</t>
+          <t>L358: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr">
         <is>
-          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="R146" s="1" t="inlineStr"/>
@@ -7808,18 +7528,18 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L368: isolated marker/symbol line :: 4</t>
+          <t>L361: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1490: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr">
         <is>
-          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
+          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
         </is>
       </c>
       <c r="R147" s="1" t="inlineStr"/>
@@ -7847,18 +7567,18 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L369: isolated marker/symbol line :: 100</t>
+          <t>L362: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr">
         <is>
-          <t>L1514: isolated marker/symbol line :: - 4</t>
+          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
         </is>
       </c>
       <c r="P148" s="1" t="inlineStr"/>
       <c r="Q148" s="1" t="inlineStr">
         <is>
-          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
+          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
         </is>
       </c>
       <c r="R148" s="1" t="inlineStr"/>
@@ -7886,18 +7606,18 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L373: isolated marker/symbol line :: 200</t>
+          <t>L363: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr">
         <is>
-          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
+          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
         </is>
       </c>
       <c r="R149" s="1" t="inlineStr"/>
@@ -7925,18 +7645,18 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L375: isolated marker/symbol line :: 0</t>
+          <t>L364: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr">
         <is>
-          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
+          <t>L1514: isolated marker/symbol line :: - 4</t>
         </is>
       </c>
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
         </is>
       </c>
       <c r="R150" s="1" t="inlineStr"/>
@@ -7964,18 +7684,18 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L376: isolated marker/symbol line :: .</t>
+          <t>L365: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr">
         <is>
-          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
+          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
         </is>
       </c>
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="R151" s="1" t="inlineStr"/>
@@ -8003,18 +7723,18 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L377: isolated marker/symbol line :: 100</t>
+          <t>L367: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr">
         <is>
-          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
+          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
         </is>
       </c>
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr">
         <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
+          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
         </is>
       </c>
       <c r="R152" s="1" t="inlineStr"/>
@@ -8042,18 +7762,18 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L378: isolated marker/symbol line :: 9</t>
+          <t>L368: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr">
         <is>
-          <t>L1524: isolated marker/symbol line :: I</t>
+          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
         </is>
       </c>
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
+          <t>L1581: punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,” 4- Snow Bird,” “- Emerald,"</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr"/>
@@ -8081,18 +7801,18 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: ç”¨</t>
+          <t>L369: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr">
         <is>
-          <t>L1590: isolated marker/symbol line :: :</t>
+          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
         </is>
       </c>
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr">
         <is>
-          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
+          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
         </is>
       </c>
       <c r="R154" s="1" t="inlineStr"/>
@@ -8120,18 +7840,18 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L380: isolated marker/symbol line :: #6</t>
+          <t>L373: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1524: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P155" s="1" t="inlineStr"/>
       <c r="Q155" s="1" t="inlineStr">
         <is>
-          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
+          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
         </is>
       </c>
       <c r="R155" s="1" t="inlineStr"/>
@@ -8159,18 +7879,18 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L381: isolated marker/symbol line :: 2</t>
+          <t>L375: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr">
         <is>
-          <t>L1593: isolated marker/symbol line :: *</t>
+          <t>L1590: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr">
         <is>
-          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
+          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
         </is>
       </c>
       <c r="R156" s="1" t="inlineStr"/>
@@ -8198,18 +7918,18 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L382: isolated marker/symbol line :: 10</t>
+          <t>L376: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr">
         <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
+          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
         </is>
       </c>
       <c r="R157" s="1" t="inlineStr"/>
@@ -8237,18 +7957,18 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L383: symbol-only separator/garbage line :: 10,</t>
+          <t>L377: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr">
         <is>
-          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
+          <t>L1593: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P158" s="1" t="inlineStr"/>
       <c r="Q158" s="1" t="inlineStr">
         <is>
-          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
+          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
         </is>
       </c>
       <c r="R158" s="1" t="inlineStr"/>
@@ -8276,18 +7996,18 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L384: isolated marker/symbol line :: "</t>
+          <t>L378: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr">
         <is>
-          <t>L1597: isolated marker/symbol line :: 1</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr">
         <is>
-          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
+          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
         </is>
       </c>
       <c r="R159" s="1" t="inlineStr"/>
@@ -8315,18 +8035,18 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L385: isolated marker/symbol line :: "</t>
+          <t>L379: stray/suspicious non-ASCII glyph(s): U+7528 CJK UNIFIED IDEOGRAPH-7528 | isolated marker/symbol line :: 用</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr">
         <is>
-          <t>L1635: isolated marker/symbol line :: n</t>
+          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
         </is>
       </c>
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
+          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr"/>
@@ -8354,18 +8074,18 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L386: isolated marker/symbol line :: 46</t>
+          <t>L380: isolated marker/symbol line :: #6</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr">
         <is>
-          <t>L1677: isolated marker/symbol line :: a.</t>
+          <t>L1597: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
+          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
         </is>
       </c>
       <c r="R161" s="1" t="inlineStr"/>
@@ -8393,18 +8113,18 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L387: isolated marker/symbol line :: 20</t>
+          <t>L381: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr">
         <is>
-          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
+          <t>L1635: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
+          <t>L1621: punctuation artifact: repeated periods :: Antoine Délorier 4 do.. ....</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr"/>
@@ -8432,18 +8152,18 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L388: symbol-only separator/garbage line :: 15,</t>
+          <t>L382: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr">
         <is>
-          <t>L1702: isolated marker/symbol line :: t</t>
+          <t>L1677: isolated marker/symbol line :: a.</t>
         </is>
       </c>
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr"/>
@@ -8471,16 +8191,20 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L389: isolated marker/symbol line :: 6</t>
+          <t>L383: symbol-only separator/garbage line :: 10,</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
         </is>
       </c>
       <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+        </is>
+      </c>
       <c r="R164" s="1" t="inlineStr"/>
       <c r="S164" s="1" t="inlineStr"/>
       <c r="T164" s="1" t="inlineStr"/>
@@ -8506,12 +8230,12 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L390: symbol-only separator/garbage line :: 2.1</t>
+          <t>L384: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr">
         <is>
-          <t>L1706: isolated marker/symbol line :: -</t>
+          <t>L1694: isolated marker/symbol line :: 9°</t>
         </is>
       </c>
       <c r="P165" s="1" t="inlineStr"/>
@@ -8541,10 +8265,14 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: 200</t>
-        </is>
-      </c>
-      <c r="O166" s="1" t="inlineStr"/>
+          <t>L385: isolated marker/symbol line :: "</t>
+        </is>
+      </c>
+      <c r="O166" s="1" t="inlineStr">
+        <is>
+          <t>L1702: isolated marker/symbol line :: t</t>
+        </is>
+      </c>
       <c r="P166" s="1" t="inlineStr"/>
       <c r="Q166" s="1" t="inlineStr"/>
       <c r="R166" s="1" t="inlineStr"/>
@@ -8572,10 +8300,14 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: 7</t>
-        </is>
-      </c>
-      <c r="O167" s="1" t="inlineStr"/>
+          <t>L386: isolated marker/symbol line :: 46</t>
+        </is>
+      </c>
+      <c r="O167" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
       <c r="P167" s="1" t="inlineStr"/>
       <c r="Q167" s="1" t="inlineStr"/>
       <c r="R167" s="1" t="inlineStr"/>
@@ -8603,10 +8335,14 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: X</t>
-        </is>
-      </c>
-      <c r="O168" s="1" t="inlineStr"/>
+          <t>L387: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
+      <c r="O168" s="1" t="inlineStr">
+        <is>
+          <t>L1706: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P168" s="1" t="inlineStr"/>
       <c r="Q168" s="1" t="inlineStr"/>
       <c r="R168" s="1" t="inlineStr"/>
@@ -8634,7 +8370,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L417: isolated marker/symbol line :: A</t>
+          <t>L388: symbol-only separator/garbage line :: 15,</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -8665,7 +8401,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L429: isolated marker/symbol line :: 0</t>
+          <t>L389: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -8696,7 +8432,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L431: isolated marker/symbol line :: 0</t>
+          <t>L390: symbol-only separator/garbage line :: 2.1</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -8727,7 +8463,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L432: isolated marker/symbol line :: 1</t>
+          <t>L392: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -8758,7 +8494,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L453: symbol-only separator/garbage line :: 1.4</t>
+          <t>L397: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -8789,7 +8525,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L455: isolated marker/symbol line :: W</t>
+          <t>L398: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -8820,7 +8556,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L462: isolated marker/symbol line :: æ°”</t>
+          <t>L417: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -8851,7 +8587,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L467: isolated marker/symbol line :: 92</t>
+          <t>L429: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -8882,7 +8618,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L471: isolated marker/symbol line :: 6</t>
+          <t>L431: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -8913,7 +8649,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 4</t>
+          <t>L432: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -8944,7 +8680,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L473: isolated marker/symbol line :: Î”</t>
+          <t>L453: symbol-only separator/garbage line :: 1.4</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -8975,7 +8711,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L475: isolated marker/symbol line :: 7</t>
+          <t>L455: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -9006,7 +8742,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L476: isolated marker/symbol line :: 8</t>
+          <t>L462: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -9037,7 +8773,7 @@
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L463: isolated marker/symbol line :: 《</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -9068,7 +8804,7 @@
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L478: isolated marker/symbol line :: Ï‰</t>
+          <t>L467: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -9099,7 +8835,7 @@
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L482: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L471: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -9130,7 +8866,7 @@
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L485: symbol-only separator/garbage line :: 8.00</t>
+          <t>L472: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -9161,7 +8897,7 @@
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L488: symbol-only separator/garbage line :: 5.00</t>
+          <t>L473: isolated marker/symbol line :: Δ</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -9192,7 +8928,7 @@
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 400</t>
+          <t>L475: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -9223,7 +8959,7 @@
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L501: symbol-only separator/garbage line :: 100.00</t>
+          <t>L476: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -9254,7 +8990,7 @@
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L505: symbol-only separator/garbage line :: 94.00</t>
+          <t>L477: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -9285,7 +9021,7 @@
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L508: isolated marker/symbol line :: "</t>
+          <t>L478: isolated marker/symbol line :: ω</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -9316,7 +9052,7 @@
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L509: isolated marker/symbol line :: F</t>
+          <t>L482: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -9347,7 +9083,7 @@
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L515: isolated marker/symbol line :: .*</t>
+          <t>L485: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -9378,7 +9114,7 @@
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: . 06</t>
+          <t>L488: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -9409,7 +9145,7 @@
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L525: isolated marker/symbol line :: *</t>
+          <t>L497: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -9440,7 +9176,7 @@
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
         <is>
-          <t>L526: isolated marker/symbol line :: 8</t>
+          <t>L501: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O195" s="1" t="inlineStr"/>
@@ -9471,7 +9207,7 @@
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
         <is>
-          <t>L527: symbol-only separator/garbage line :: 1.00</t>
+          <t>L505: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O196" s="1" t="inlineStr"/>
@@ -9502,7 +9238,7 @@
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
         <is>
-          <t>L529: isolated marker/symbol line :: .</t>
+          <t>L508: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O197" s="1" t="inlineStr"/>
@@ -9533,7 +9269,7 @@
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
         <is>
-          <t>L537: isolated marker/symbol line :: 2</t>
+          <t>L509: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O198" s="1" t="inlineStr"/>
@@ -9564,7 +9300,7 @@
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
         <is>
-          <t>L542: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L515: isolated marker/symbol line :: .*</t>
         </is>
       </c>
       <c r="O199" s="1" t="inlineStr"/>
@@ -9595,7 +9331,7 @@
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
         <is>
-          <t>L545: symbol-only separator/garbage line :: 2.00</t>
+          <t>L516: symbol-only separator/garbage line :: . 06</t>
         </is>
       </c>
       <c r="O200" s="1" t="inlineStr"/>
@@ -9626,7 +9362,7 @@
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
         <is>
-          <t>L549: symbol-only separator/garbage line :: 1600</t>
+          <t>L525: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O201" s="1" t="inlineStr"/>
@@ -9657,7 +9393,7 @@
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
         <is>
-          <t>L554: isolated marker/symbol line :: 8</t>
+          <t>L526: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O202" s="1" t="inlineStr"/>
@@ -9688,7 +9424,7 @@
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
         <is>
-          <t>L555: isolated marker/symbol line :: 85</t>
+          <t>L527: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O203" s="1" t="inlineStr"/>
@@ -9719,7 +9455,7 @@
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
         <is>
-          <t>L560: symbol-only separator/garbage line :: 1.00</t>
+          <t>L529: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O204" s="1" t="inlineStr"/>
@@ -9750,7 +9486,7 @@
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
         <is>
-          <t>L564: symbol-only separator/garbage line :: 2.00</t>
+          <t>L537: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O205" s="1" t="inlineStr"/>
@@ -9781,7 +9517,7 @@
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
         <is>
-          <t>L567: symbol-only separator/garbage line :: 5.00</t>
+          <t>L542: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O206" s="1" t="inlineStr"/>
@@ -9812,7 +9548,7 @@
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
         <is>
-          <t>L568: isolated marker/symbol line :: 0</t>
+          <t>L545: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O207" s="1" t="inlineStr"/>
@@ -9843,7 +9579,7 @@
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
         <is>
-          <t>L569: symbol-only separator/garbage line :: 31.31</t>
+          <t>L549: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O208" s="1" t="inlineStr"/>
@@ -9874,7 +9610,7 @@
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
         <is>
-          <t>L574: isolated marker/symbol line :: $</t>
+          <t>L554: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O209" s="1" t="inlineStr"/>
@@ -9905,7 +9641,7 @@
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
         <is>
-          <t>L575: isolated marker/symbol line :: 4</t>
+          <t>L555: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O210" s="1" t="inlineStr"/>
@@ -9936,7 +9672,7 @@
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
         <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L560: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O211" s="1" t="inlineStr"/>
@@ -9967,7 +9703,7 @@
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
         <is>
-          <t>L578: symbol-only separator/garbage line :: 9555</t>
+          <t>L564: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O212" s="1" t="inlineStr"/>
@@ -9998,7 +9734,7 @@
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
         <is>
-          <t>L579: isolated marker/symbol line :: 95</t>
+          <t>L567: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O213" s="1" t="inlineStr"/>
@@ -10029,7 +9765,7 @@
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
         <is>
-          <t>L581: isolated marker/symbol line :: 9</t>
+          <t>L568: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O214" s="1" t="inlineStr"/>
@@ -10060,7 +9796,7 @@
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
         <is>
-          <t>L582: isolated marker/symbol line :: 4</t>
+          <t>L569: symbol-only separator/garbage line :: 31.31</t>
         </is>
       </c>
       <c r="O215" s="1" t="inlineStr"/>
@@ -10091,7 +9827,7 @@
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
         <is>
-          <t>L588: isolated marker/symbol line :: 1</t>
+          <t>L574: isolated marker/symbol line :: $</t>
         </is>
       </c>
       <c r="O216" s="1" t="inlineStr"/>
@@ -10122,7 +9858,7 @@
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
         <is>
-          <t>L589: symbol-only separator/garbage line :: 1,. 20</t>
+          <t>L575: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O217" s="1" t="inlineStr"/>
@@ -10153,7 +9889,7 @@
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
         <is>
-          <t>L592: symbol-only separator/garbage line :: 3, 00</t>
+          <t>L576: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O218" s="1" t="inlineStr"/>
@@ -10184,7 +9920,7 @@
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
         <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L578: symbol-only separator/garbage line :: 9555</t>
         </is>
       </c>
       <c r="O219" s="1" t="inlineStr"/>
@@ -10215,7 +9951,7 @@
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
         <is>
-          <t>L594: symbol-only separator/garbage line :: 91.30</t>
+          <t>L579: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O220" s="1" t="inlineStr"/>
@@ -10246,7 +9982,7 @@
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
         <is>
-          <t>L597: symbol-only separator/garbage line :: 300.00</t>
+          <t>L581: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O221" s="1" t="inlineStr"/>
@@ -10277,7 +10013,7 @@
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
         <is>
-          <t>L599: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "1000" vs "100 00" :: 1000</t>
+          <t>L582: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O222" s="1" t="inlineStr"/>
@@ -10308,7 +10044,7 @@
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
         <is>
-          <t>L601: symbol-only separator/garbage line :: 80.00</t>
+          <t>L588: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O223" s="1" t="inlineStr"/>
@@ -10339,7 +10075,7 @@
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
         <is>
-          <t>L602: symbol-only separator/garbage line :: 480.00</t>
+          <t>L589: symbol-only separator/garbage line :: 1,. 20</t>
         </is>
       </c>
       <c r="O224" s="1" t="inlineStr"/>
@@ -10370,7 +10106,7 @@
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
         <is>
-          <t>L605: symbol-only separator/garbage line :: 2021.15</t>
+          <t>L592: symbol-only separator/garbage line :: 3, 00</t>
         </is>
       </c>
       <c r="O225" s="1" t="inlineStr"/>
@@ -10401,7 +10137,7 @@
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
         <is>
-          <t>L606: symbol-only separator/garbage line :: $3542.404</t>
+          <t>L593: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O226" s="1" t="inlineStr"/>
@@ -10432,7 +10168,7 @@
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
         <is>
-          <t>L612: isolated marker/symbol line :: ***</t>
+          <t>L594: symbol-only separator/garbage line :: 91.30</t>
         </is>
       </c>
       <c r="O227" s="1" t="inlineStr"/>
@@ -10463,7 +10199,7 @@
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
         <is>
-          <t>L613: symbol-only separator/garbage line :: 6.90</t>
+          <t>L597: symbol-only separator/garbage line :: 300.00</t>
         </is>
       </c>
       <c r="O228" s="1" t="inlineStr"/>
@@ -10494,7 +10230,7 @@
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
         <is>
-          <t>L620: isolated marker/symbol line :: 20</t>
+          <t>L599: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "1000" vs "100 00" :: 1000</t>
         </is>
       </c>
       <c r="O229" s="1" t="inlineStr"/>
@@ -10525,7 +10261,7 @@
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
         <is>
-          <t>L622: symbol-only separator/garbage line :: 14.05</t>
+          <t>L601: symbol-only separator/garbage line :: 80.00</t>
         </is>
       </c>
       <c r="O230" s="1" t="inlineStr"/>
@@ -10556,7 +10292,7 @@
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
         <is>
-          <t>L625: symbol-only separator/garbage line :: ***********</t>
+          <t>L602: symbol-only separator/garbage line :: 480.00</t>
         </is>
       </c>
       <c r="O231" s="1" t="inlineStr"/>
@@ -10587,7 +10323,7 @@
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
         <is>
-          <t>L626: symbol-only separator/garbage line :: ******</t>
+          <t>L605: symbol-only separator/garbage line :: 2021.15</t>
         </is>
       </c>
       <c r="O232" s="1" t="inlineStr"/>
@@ -10618,7 +10354,7 @@
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 02.00</t>
+          <t>L606: symbol-only separator/garbage line :: $3542.404</t>
         </is>
       </c>
       <c r="O233" s="1" t="inlineStr"/>
@@ -10649,7 +10385,7 @@
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
         <is>
-          <t>L629: isolated marker/symbol line :: 15</t>
+          <t>L612: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O234" s="1" t="inlineStr"/>
@@ -10680,7 +10416,7 @@
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
         <is>
-          <t>L630: isolated marker/symbol line :: C</t>
+          <t>L613: symbol-only separator/garbage line :: 6.90</t>
         </is>
       </c>
       <c r="O235" s="1" t="inlineStr"/>
@@ -10711,7 +10447,7 @@
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
         <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L620: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O236" s="1" t="inlineStr"/>
@@ -10742,7 +10478,7 @@
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
         <is>
-          <t>L637: isolated marker/symbol line :: D</t>
+          <t>L622: symbol-only separator/garbage line :: 14.05</t>
         </is>
       </c>
       <c r="O237" s="1" t="inlineStr"/>
@@ -10773,7 +10509,7 @@
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: a.</t>
+          <t>L625: symbol-only separator/garbage line :: ***********</t>
         </is>
       </c>
       <c r="O238" s="1" t="inlineStr"/>
@@ -10804,7 +10540,7 @@
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
         <is>
-          <t>L643: isolated marker/symbol line :: d.</t>
+          <t>L626: symbol-only separator/garbage line :: ******</t>
         </is>
       </c>
       <c r="O239" s="1" t="inlineStr"/>
@@ -10835,7 +10571,7 @@
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
         <is>
-          <t>L662: isolated marker/symbol line :: 2</t>
+          <t>L627: symbol-only separator/garbage line :: 02.00</t>
         </is>
       </c>
       <c r="O240" s="1" t="inlineStr"/>
@@ -10866,7 +10602,7 @@
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
         <is>
-          <t>L682: isolated marker/symbol line :: A</t>
+          <t>L629: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O241" s="1" t="inlineStr"/>
@@ -10897,7 +10633,7 @@
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
         <is>
-          <t>L696: isolated marker/symbol line :: 1</t>
+          <t>L630: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O242" s="1" t="inlineStr"/>
@@ -10928,7 +10664,7 @@
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
         <is>
-          <t>L701: symbol-only separator/garbage line :: 9.50</t>
+          <t>L636: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O243" s="1" t="inlineStr"/>
@@ -10959,7 +10695,7 @@
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L637: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O244" s="1" t="inlineStr"/>
@@ -10990,7 +10726,7 @@
       <c r="M245" s="1" t="inlineStr"/>
       <c r="N245" s="1" t="inlineStr">
         <is>
-          <t>L705: symbol-only separator/garbage line :: 40.00</t>
+          <t>L642: isolated marker/symbol line :: a.</t>
         </is>
       </c>
       <c r="O245" s="1" t="inlineStr"/>
@@ -11021,7 +10757,7 @@
       <c r="M246" s="1" t="inlineStr"/>
       <c r="N246" s="1" t="inlineStr">
         <is>
-          <t>L707: symbol-only separator/garbage line :: 1600</t>
+          <t>L643: isolated marker/symbol line :: d.</t>
         </is>
       </c>
       <c r="O246" s="1" t="inlineStr"/>
@@ -11052,7 +10788,7 @@
       <c r="M247" s="1" t="inlineStr"/>
       <c r="N247" s="1" t="inlineStr">
         <is>
-          <t>L709: symbol-only separator/garbage line :: 32.00</t>
+          <t>L662: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O247" s="1" t="inlineStr"/>
@@ -11083,7 +10819,7 @@
       <c r="M248" s="1" t="inlineStr"/>
       <c r="N248" s="1" t="inlineStr">
         <is>
-          <t>L711: symbol-only separator/garbage line :: 50.00</t>
+          <t>L682: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O248" s="1" t="inlineStr"/>
@@ -11114,7 +10850,7 @@
       <c r="M249" s="1" t="inlineStr"/>
       <c r="N249" s="1" t="inlineStr">
         <is>
-          <t>L713: isolated marker/symbol line :: 337</t>
+          <t>L696: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O249" s="1" t="inlineStr"/>
@@ -11145,7 +10881,7 @@
       <c r="M250" s="1" t="inlineStr"/>
       <c r="N250" s="1" t="inlineStr">
         <is>
-          <t>L715: isolated marker/symbol line :: 36</t>
+          <t>L701: symbol-only separator/garbage line :: 9.50</t>
         </is>
       </c>
       <c r="O250" s="1" t="inlineStr"/>
@@ -11176,7 +10912,7 @@
       <c r="M251" s="1" t="inlineStr"/>
       <c r="N251" s="1" t="inlineStr">
         <is>
-          <t>L717: symbol-only separator/garbage line :: 5.91</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr"/>
@@ -11207,7 +10943,7 @@
       <c r="M252" s="1" t="inlineStr"/>
       <c r="N252" s="1" t="inlineStr">
         <is>
-          <t>L718: symbol-only separator/garbage line :: 5.21</t>
+          <t>L705: symbol-only separator/garbage line :: 40.00</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr"/>
@@ -11238,7 +10974,7 @@
       <c r="M253" s="1" t="inlineStr"/>
       <c r="N253" s="1" t="inlineStr">
         <is>
-          <t>L720: isolated marker/symbol line :: 130</t>
+          <t>L707: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr"/>
@@ -11269,7 +11005,7 @@
       <c r="M254" s="1" t="inlineStr"/>
       <c r="N254" s="1" t="inlineStr">
         <is>
-          <t>L721: isolated marker/symbol line :: .</t>
+          <t>L709: symbol-only separator/garbage line :: 32.00</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr"/>
@@ -11300,7 +11036,7 @@
       <c r="M255" s="1" t="inlineStr"/>
       <c r="N255" s="1" t="inlineStr">
         <is>
-          <t>L723: symbol-only separator/garbage line :: 21.00</t>
+          <t>L711: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O255" s="1" t="inlineStr"/>
@@ -11331,7 +11067,7 @@
       <c r="M256" s="1" t="inlineStr"/>
       <c r="N256" s="1" t="inlineStr">
         <is>
-          <t>L727: symbol-only separator/garbage line :: 69.16</t>
+          <t>L713: isolated marker/symbol line :: 337</t>
         </is>
       </c>
       <c r="O256" s="1" t="inlineStr"/>
@@ -11362,7 +11098,7 @@
       <c r="M257" s="1" t="inlineStr"/>
       <c r="N257" s="1" t="inlineStr">
         <is>
-          <t>L728: isolated marker/symbol line :: w</t>
+          <t>L715: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O257" s="1" t="inlineStr"/>
@@ -11393,7 +11129,7 @@
       <c r="M258" s="1" t="inlineStr"/>
       <c r="N258" s="1" t="inlineStr">
         <is>
-          <t>L730: symbol-only separator/garbage line :: 24.75</t>
+          <t>L717: symbol-only separator/garbage line :: 5.91</t>
         </is>
       </c>
       <c r="O258" s="1" t="inlineStr"/>
@@ -11424,7 +11160,7 @@
       <c r="M259" s="1" t="inlineStr"/>
       <c r="N259" s="1" t="inlineStr">
         <is>
-          <t>L731: isolated marker/symbol line :: $O</t>
+          <t>L718: symbol-only separator/garbage line :: 5.21</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr"/>
@@ -11455,7 +11191,7 @@
       <c r="M260" s="1" t="inlineStr"/>
       <c r="N260" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: 0</t>
+          <t>L720: isolated marker/symbol line :: 130</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr"/>
@@ -11486,7 +11222,7 @@
       <c r="M261" s="1" t="inlineStr"/>
       <c r="N261" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: -</t>
+          <t>L721: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr"/>
@@ -11517,7 +11253,7 @@
       <c r="M262" s="1" t="inlineStr"/>
       <c r="N262" s="1" t="inlineStr">
         <is>
-          <t>L737: isolated marker/symbol line :: 4</t>
+          <t>L723: symbol-only separator/garbage line :: 21.00</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr"/>
@@ -11548,7 +11284,7 @@
       <c r="M263" s="1" t="inlineStr"/>
       <c r="N263" s="1" t="inlineStr">
         <is>
-          <t>L739: isolated marker/symbol line :: 150</t>
+          <t>L727: symbol-only separator/garbage line :: 69.16</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr"/>
@@ -11579,7 +11315,7 @@
       <c r="M264" s="1" t="inlineStr"/>
       <c r="N264" s="1" t="inlineStr">
         <is>
-          <t>L740: symbol-only separator/garbage line :: 4.50</t>
+          <t>L728: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="O264" s="1" t="inlineStr"/>
@@ -11610,7 +11346,7 @@
       <c r="M265" s="1" t="inlineStr"/>
       <c r="N265" s="1" t="inlineStr">
         <is>
-          <t>L745: symbol-only separator/garbage line :: 36.00</t>
+          <t>L730: symbol-only separator/garbage line :: 24.75</t>
         </is>
       </c>
       <c r="O265" s="1" t="inlineStr"/>
@@ -11641,7 +11377,7 @@
       <c r="M266" s="1" t="inlineStr"/>
       <c r="N266" s="1" t="inlineStr">
         <is>
-          <t>L747: isolated marker/symbol line :: 2</t>
+          <t>L731: isolated marker/symbol line :: $O</t>
         </is>
       </c>
       <c r="O266" s="1" t="inlineStr"/>
@@ -11672,7 +11408,7 @@
       <c r="M267" s="1" t="inlineStr"/>
       <c r="N267" s="1" t="inlineStr">
         <is>
-          <t>L749: symbol-only separator/garbage line :: 3900</t>
+          <t>L732: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O267" s="1" t="inlineStr"/>
@@ -11703,7 +11439,7 @@
       <c r="M268" s="1" t="inlineStr"/>
       <c r="N268" s="1" t="inlineStr">
         <is>
-          <t>L752: symbol-only separator/garbage line :: 39.00</t>
+          <t>L734: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O268" s="1" t="inlineStr"/>
@@ -11734,7 +11470,7 @@
       <c r="M269" s="1" t="inlineStr"/>
       <c r="N269" s="1" t="inlineStr">
         <is>
-          <t>L754: isolated marker/symbol line :: 3</t>
+          <t>L737: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O269" s="1" t="inlineStr"/>
@@ -11765,7 +11501,7 @@
       <c r="M270" s="1" t="inlineStr"/>
       <c r="N270" s="1" t="inlineStr">
         <is>
-          <t>L755: isolated marker/symbol line :: X</t>
+          <t>L739: isolated marker/symbol line :: 150</t>
         </is>
       </c>
       <c r="O270" s="1" t="inlineStr"/>
@@ -11796,7 +11532,7 @@
       <c r="M271" s="1" t="inlineStr"/>
       <c r="N271" s="1" t="inlineStr">
         <is>
-          <t>L757: symbol-only separator/garbage line :: 1.60</t>
+          <t>L740: symbol-only separator/garbage line :: 4.50</t>
         </is>
       </c>
       <c r="O271" s="1" t="inlineStr"/>
@@ -11827,7 +11563,7 @@
       <c r="M272" s="1" t="inlineStr"/>
       <c r="N272" s="1" t="inlineStr">
         <is>
-          <t>L760: isolated marker/symbol line :: 7</t>
+          <t>L745: symbol-only separator/garbage line :: 36.00</t>
         </is>
       </c>
       <c r="O272" s="1" t="inlineStr"/>
@@ -11858,7 +11594,7 @@
       <c r="M273" s="1" t="inlineStr"/>
       <c r="N273" s="1" t="inlineStr">
         <is>
-          <t>L761: symbol-only separator/garbage line :: 7.07</t>
+          <t>L747: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O273" s="1" t="inlineStr"/>
@@ -11889,7 +11625,7 @@
       <c r="M274" s="1" t="inlineStr"/>
       <c r="N274" s="1" t="inlineStr">
         <is>
-          <t>L763: symbol-only separator/garbage line :: 4.50</t>
+          <t>L749: symbol-only separator/garbage line :: 3900</t>
         </is>
       </c>
       <c r="O274" s="1" t="inlineStr"/>
@@ -11920,7 +11656,7 @@
       <c r="M275" s="1" t="inlineStr"/>
       <c r="N275" s="1" t="inlineStr">
         <is>
-          <t>L769: isolated marker/symbol line :: 2</t>
+          <t>L752: symbol-only separator/garbage line :: 39.00</t>
         </is>
       </c>
       <c r="O275" s="1" t="inlineStr"/>
@@ -11951,7 +11687,7 @@
       <c r="M276" s="1" t="inlineStr"/>
       <c r="N276" s="1" t="inlineStr">
         <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
+          <t>L754: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O276" s="1" t="inlineStr"/>
@@ -11982,7 +11718,7 @@
       <c r="M277" s="1" t="inlineStr"/>
       <c r="N277" s="1" t="inlineStr">
         <is>
-          <t>L777: isolated marker/symbol line :: L</t>
+          <t>L755: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O277" s="1" t="inlineStr"/>
@@ -12013,7 +11749,7 @@
       <c r="M278" s="1" t="inlineStr"/>
       <c r="N278" s="1" t="inlineStr">
         <is>
-          <t>L778: isolated marker/symbol line :: 1</t>
+          <t>L757: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="O278" s="1" t="inlineStr"/>
@@ -12044,7 +11780,7 @@
       <c r="M279" s="1" t="inlineStr"/>
       <c r="N279" s="1" t="inlineStr">
         <is>
-          <t>L812: isolated marker/symbol line :: 15</t>
+          <t>L760: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O279" s="1" t="inlineStr"/>
@@ -12075,7 +11811,7 @@
       <c r="M280" s="1" t="inlineStr"/>
       <c r="N280" s="1" t="inlineStr">
         <is>
-          <t>L830: isolated marker/symbol line :: 4</t>
+          <t>L761: symbol-only separator/garbage line :: 7.07</t>
         </is>
       </c>
       <c r="O280" s="1" t="inlineStr"/>
@@ -12106,7 +11842,7 @@
       <c r="M281" s="1" t="inlineStr"/>
       <c r="N281" s="1" t="inlineStr">
         <is>
-          <t>L846: isolated marker/symbol line :: 4</t>
+          <t>L763: symbol-only separator/garbage line :: 4.50</t>
         </is>
       </c>
       <c r="O281" s="1" t="inlineStr"/>
@@ -12137,7 +11873,7 @@
       <c r="M282" s="1" t="inlineStr"/>
       <c r="N282" s="1" t="inlineStr">
         <is>
-          <t>L868: symbol-only separator/garbage line :: 1961.</t>
+          <t>L767: symbol-only separator/garbage line :: · 1.00</t>
         </is>
       </c>
       <c r="O282" s="1" t="inlineStr"/>
@@ -12168,7 +11904,7 @@
       <c r="M283" s="1" t="inlineStr"/>
       <c r="N283" s="1" t="inlineStr">
         <is>
-          <t>L869: isolated marker/symbol line :: 9</t>
+          <t>L769: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O283" s="1" t="inlineStr"/>
@@ -12199,7 +11935,7 @@
       <c r="M284" s="1" t="inlineStr"/>
       <c r="N284" s="1" t="inlineStr">
         <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L770: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="O284" s="1" t="inlineStr"/>
@@ -12230,7 +11966,7 @@
       <c r="M285" s="1" t="inlineStr"/>
       <c r="N285" s="1" t="inlineStr">
         <is>
-          <t>L873: isolated marker/symbol line :: "</t>
+          <t>L777: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O285" s="1" t="inlineStr"/>
@@ -12261,7 +11997,7 @@
       <c r="M286" s="1" t="inlineStr"/>
       <c r="N286" s="1" t="inlineStr">
         <is>
-          <t>L874: isolated marker/symbol line :: .</t>
+          <t>L778: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O286" s="1" t="inlineStr"/>
@@ -12292,7 +12028,7 @@
       <c r="M287" s="1" t="inlineStr"/>
       <c r="N287" s="1" t="inlineStr">
         <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
+          <t>L812: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O287" s="1" t="inlineStr"/>
@@ -12323,7 +12059,7 @@
       <c r="M288" s="1" t="inlineStr"/>
       <c r="N288" s="1" t="inlineStr">
         <is>
-          <t>L877: isolated marker/symbol line :: 8</t>
+          <t>L830: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O288" s="1" t="inlineStr"/>
@@ -12354,7 +12090,7 @@
       <c r="M289" s="1" t="inlineStr"/>
       <c r="N289" s="1" t="inlineStr">
         <is>
-          <t>L880: isolated marker/symbol line :: 13</t>
+          <t>L846: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O289" s="1" t="inlineStr"/>
@@ -12385,7 +12121,7 @@
       <c r="M290" s="1" t="inlineStr"/>
       <c r="N290" s="1" t="inlineStr">
         <is>
-          <t>L881: isolated marker/symbol line :: "</t>
+          <t>L868: symbol-only separator/garbage line :: 1961.</t>
         </is>
       </c>
       <c r="O290" s="1" t="inlineStr"/>
@@ -12416,7 +12152,7 @@
       <c r="M291" s="1" t="inlineStr"/>
       <c r="N291" s="1" t="inlineStr">
         <is>
-          <t>L882: isolated marker/symbol line :: 4</t>
+          <t>L869: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O291" s="1" t="inlineStr"/>
@@ -12447,7 +12183,7 @@
       <c r="M292" s="1" t="inlineStr"/>
       <c r="N292" s="1" t="inlineStr">
         <is>
-          <t>L884: isolated marker/symbol line :: 14</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O292" s="1" t="inlineStr"/>
@@ -12478,7 +12214,7 @@
       <c r="M293" s="1" t="inlineStr"/>
       <c r="N293" s="1" t="inlineStr">
         <is>
-          <t>L885: isolated marker/symbol line :: 64</t>
+          <t>L873: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O293" s="1" t="inlineStr"/>
@@ -12509,7 +12245,7 @@
       <c r="M294" s="1" t="inlineStr"/>
       <c r="N294" s="1" t="inlineStr">
         <is>
-          <t>L887: isolated marker/symbol line :: 1</t>
+          <t>L874: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O294" s="1" t="inlineStr"/>
@@ -12540,7 +12276,7 @@
       <c r="M295" s="1" t="inlineStr"/>
       <c r="N295" s="1" t="inlineStr">
         <is>
-          <t>L888: isolated marker/symbol line :: "</t>
+          <t>L875: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
         </is>
       </c>
       <c r="O295" s="1" t="inlineStr"/>
@@ -12571,7 +12307,7 @@
       <c r="M296" s="1" t="inlineStr"/>
       <c r="N296" s="1" t="inlineStr">
         <is>
-          <t>L890: isolated marker/symbol line :: 2</t>
+          <t>L877: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O296" s="1" t="inlineStr"/>
@@ -12602,7 +12338,7 @@
       <c r="M297" s="1" t="inlineStr"/>
       <c r="N297" s="1" t="inlineStr">
         <is>
-          <t>L892: isolated marker/symbol line :: "</t>
+          <t>L880: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O297" s="1" t="inlineStr"/>
@@ -12633,7 +12369,7 @@
       <c r="M298" s="1" t="inlineStr"/>
       <c r="N298" s="1" t="inlineStr">
         <is>
-          <t>L894: isolated marker/symbol line :: 6</t>
+          <t>L881: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O298" s="1" t="inlineStr"/>
@@ -12664,7 +12400,7 @@
       <c r="M299" s="1" t="inlineStr"/>
       <c r="N299" s="1" t="inlineStr">
         <is>
-          <t>L895: isolated marker/symbol line :: 28</t>
+          <t>L882: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O299" s="1" t="inlineStr"/>
@@ -12695,7 +12431,7 @@
       <c r="M300" s="1" t="inlineStr"/>
       <c r="N300" s="1" t="inlineStr">
         <is>
-          <t>L897: isolated marker/symbol line :: 4</t>
+          <t>L884: isolated marker/symbol line :: 14</t>
         </is>
       </c>
       <c r="O300" s="1" t="inlineStr"/>
@@ -12726,7 +12462,7 @@
       <c r="M301" s="1" t="inlineStr"/>
       <c r="N301" s="1" t="inlineStr">
         <is>
-          <t>L899: isolated marker/symbol line :: 6</t>
+          <t>L885: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O301" s="1" t="inlineStr"/>
@@ -12757,7 +12493,7 @@
       <c r="M302" s="1" t="inlineStr"/>
       <c r="N302" s="1" t="inlineStr">
         <is>
-          <t>L901: isolated marker/symbol line :: 4</t>
+          <t>L887: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O302" s="1" t="inlineStr"/>
@@ -12788,7 +12524,7 @@
       <c r="M303" s="1" t="inlineStr"/>
       <c r="N303" s="1" t="inlineStr">
         <is>
-          <t>L905: isolated marker/symbol line :: 4</t>
+          <t>L888: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O303" s="1" t="inlineStr"/>
@@ -12819,7 +12555,7 @@
       <c r="M304" s="1" t="inlineStr"/>
       <c r="N304" s="1" t="inlineStr">
         <is>
-          <t>L907: isolated marker/symbol line :: " 6</t>
+          <t>L890: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O304" s="1" t="inlineStr"/>
@@ -12850,7 +12586,7 @@
       <c r="M305" s="1" t="inlineStr"/>
       <c r="N305" s="1" t="inlineStr">
         <is>
-          <t>L912: isolated marker/symbol line :: #</t>
+          <t>L892: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O305" s="1" t="inlineStr"/>
@@ -12881,7 +12617,7 @@
       <c r="M306" s="1" t="inlineStr"/>
       <c r="N306" s="1" t="inlineStr">
         <is>
-          <t>L916: isolated marker/symbol line :: .</t>
+          <t>L894: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O306" s="1" t="inlineStr"/>
@@ -12912,7 +12648,7 @@
       <c r="M307" s="1" t="inlineStr"/>
       <c r="N307" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 8</t>
+          <t>L895: isolated marker/symbol line :: 28</t>
         </is>
       </c>
       <c r="O307" s="1" t="inlineStr"/>
@@ -12943,7 +12679,7 @@
       <c r="M308" s="1" t="inlineStr"/>
       <c r="N308" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: 24</t>
+          <t>L897: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O308" s="1" t="inlineStr"/>
@@ -12974,7 +12710,7 @@
       <c r="M309" s="1" t="inlineStr"/>
       <c r="N309" s="1" t="inlineStr">
         <is>
-          <t>L922: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L899: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O309" s="1" t="inlineStr"/>
@@ -13005,7 +12741,7 @@
       <c r="M310" s="1" t="inlineStr"/>
       <c r="N310" s="1" t="inlineStr">
         <is>
-          <t>L923: isolated marker/symbol line :: 4</t>
+          <t>L901: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O310" s="1" t="inlineStr"/>
@@ -13036,7 +12772,7 @@
       <c r="M311" s="1" t="inlineStr"/>
       <c r="N311" s="1" t="inlineStr">
         <is>
-          <t>L936: isolated marker/symbol line :: 89</t>
+          <t>L903: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O311" s="1" t="inlineStr"/>
@@ -13067,7 +12803,7 @@
       <c r="M312" s="1" t="inlineStr"/>
       <c r="N312" s="1" t="inlineStr">
         <is>
-          <t>L959: isolated marker/symbol line :: 4</t>
+          <t>L905: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O312" s="1" t="inlineStr"/>
@@ -13098,7 +12834,7 @@
       <c r="M313" s="1" t="inlineStr"/>
       <c r="N313" s="1" t="inlineStr">
         <is>
-          <t>L970: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L907: isolated marker/symbol line :: " 6</t>
         </is>
       </c>
       <c r="O313" s="1" t="inlineStr"/>
@@ -13129,7 +12865,7 @@
       <c r="M314" s="1" t="inlineStr"/>
       <c r="N314" s="1" t="inlineStr">
         <is>
-          <t>L971: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A8 DIAERESIS | isolated marker/symbol line :: å™¨</t>
+          <t>L912: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="O314" s="1" t="inlineStr"/>
@@ -13160,7 +12896,7 @@
       <c r="M315" s="1" t="inlineStr"/>
       <c r="N315" s="1" t="inlineStr">
         <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L916: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O315" s="1" t="inlineStr"/>
@@ -13191,7 +12927,7 @@
       <c r="M316" s="1" t="inlineStr"/>
       <c r="N316" s="1" t="inlineStr">
         <is>
-          <t>L986: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é�</t>
+          <t>L920: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O316" s="1" t="inlineStr"/>
@@ -13222,7 +12958,7 @@
       <c r="M317" s="1" t="inlineStr"/>
       <c r="N317" s="1" t="inlineStr">
         <is>
-          <t>L987: isolated marker/symbol line :: 8</t>
+          <t>L921: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O317" s="1" t="inlineStr"/>
@@ -13253,7 +12989,7 @@
       <c r="M318" s="1" t="inlineStr"/>
       <c r="N318" s="1" t="inlineStr">
         <is>
-          <t>L1003: isolated marker/symbol line :: 4</t>
+          <t>L922: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O318" s="1" t="inlineStr"/>
@@ -13284,7 +13020,7 @@
       <c r="M319" s="1" t="inlineStr"/>
       <c r="N319" s="1" t="inlineStr">
         <is>
-          <t>L1009: isolated marker/symbol line :: P</t>
+          <t>L923: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O319" s="1" t="inlineStr"/>
@@ -13315,7 +13051,7 @@
       <c r="M320" s="1" t="inlineStr"/>
       <c r="N320" s="1" t="inlineStr">
         <is>
-          <t>L1011: isolated marker/symbol line :: .</t>
+          <t>L936: isolated marker/symbol line :: 89</t>
         </is>
       </c>
       <c r="O320" s="1" t="inlineStr"/>
@@ -13346,7 +13082,7 @@
       <c r="M321" s="1" t="inlineStr"/>
       <c r="N321" s="1" t="inlineStr">
         <is>
-          <t>L1012: isolated marker/symbol line :: 2</t>
+          <t>L959: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O321" s="1" t="inlineStr"/>
@@ -13377,7 +13113,7 @@
       <c r="M322" s="1" t="inlineStr"/>
       <c r="N322" s="1" t="inlineStr">
         <is>
-          <t>L1015: isolated marker/symbol line :: :</t>
+          <t>L970: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O322" s="1" t="inlineStr"/>
@@ -13408,7 +13144,7 @@
       <c r="M323" s="1" t="inlineStr"/>
       <c r="N323" s="1" t="inlineStr">
         <is>
-          <t>L1031: isolated marker/symbol line :: 44</t>
+          <t>L971: stray/suspicious non-ASCII glyph(s): U+5668 CJK UNIFIED IDEOGRAPH-5668 | isolated marker/symbol line :: 器</t>
         </is>
       </c>
       <c r="O323" s="1" t="inlineStr"/>
@@ -13439,7 +13175,7 @@
       <c r="M324" s="1" t="inlineStr"/>
       <c r="N324" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: 000</t>
+          <t>L972: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O324" s="1" t="inlineStr"/>
@@ -13470,7 +13206,7 @@
       <c r="M325" s="1" t="inlineStr"/>
       <c r="N325" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: -</t>
+          <t>L973: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O325" s="1" t="inlineStr"/>
@@ -13501,7 +13237,7 @@
       <c r="M326" s="1" t="inlineStr"/>
       <c r="N326" s="1" t="inlineStr">
         <is>
-          <t>L1035: isolated marker/symbol line :: .</t>
+          <t>L986: stray/suspicious non-ASCII glyph(s): U+9760 CJK UNIFIED IDEOGRAPH-9760 | isolated marker/symbol line :: 靠</t>
         </is>
       </c>
       <c r="O326" s="1" t="inlineStr"/>
@@ -13532,7 +13268,7 @@
       <c r="M327" s="1" t="inlineStr"/>
       <c r="N327" s="1" t="inlineStr">
         <is>
-          <t>L1053: isolated marker/symbol line :: 2</t>
+          <t>L987: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O327" s="1" t="inlineStr"/>
@@ -13563,7 +13299,7 @@
       <c r="M328" s="1" t="inlineStr"/>
       <c r="N328" s="1" t="inlineStr">
         <is>
-          <t>L1057: isolated marker/symbol line :: 7</t>
+          <t>L988: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="O328" s="1" t="inlineStr"/>
@@ -13594,7 +13330,7 @@
       <c r="M329" s="1" t="inlineStr"/>
       <c r="N329" s="1" t="inlineStr">
         <is>
-          <t>L1060: isolated marker/symbol line :: 19</t>
+          <t>L1003: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O329" s="1" t="inlineStr"/>
@@ -13625,7 +13361,7 @@
       <c r="M330" s="1" t="inlineStr"/>
       <c r="N330" s="1" t="inlineStr">
         <is>
-          <t>L1061: isolated marker/symbol line :: 4</t>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O330" s="1" t="inlineStr"/>
@@ -13656,7 +13392,7 @@
       <c r="M331" s="1" t="inlineStr"/>
       <c r="N331" s="1" t="inlineStr">
         <is>
-          <t>L1062: isolated marker/symbol line :: 6</t>
+          <t>L1009: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O331" s="1" t="inlineStr"/>
@@ -13687,7 +13423,7 @@
       <c r="M332" s="1" t="inlineStr"/>
       <c r="N332" s="1" t="inlineStr">
         <is>
-          <t>L1063: isolated marker/symbol line :: 66</t>
+          <t>L1011: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O332" s="1" t="inlineStr"/>
@@ -13718,7 +13454,7 @@
       <c r="M333" s="1" t="inlineStr"/>
       <c r="N333" s="1" t="inlineStr">
         <is>
-          <t>L1064: isolated marker/symbol line :: 200</t>
+          <t>L1012: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O333" s="1" t="inlineStr"/>
@@ -13749,7 +13485,7 @@
       <c r="M334" s="1" t="inlineStr"/>
       <c r="N334" s="1" t="inlineStr">
         <is>
-          <t>L1066: symbol-only separator/garbage line :: 25,</t>
+          <t>L1015: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O334" s="1" t="inlineStr"/>
@@ -13780,7 +13516,7 @@
       <c r="M335" s="1" t="inlineStr"/>
       <c r="N335" s="1" t="inlineStr">
         <is>
-          <t>L1067: isolated marker/symbol line :: .</t>
+          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: ± 5</t>
         </is>
       </c>
       <c r="O335" s="1" t="inlineStr"/>
@@ -13811,7 +13547,7 @@
       <c r="M336" s="1" t="inlineStr"/>
       <c r="N336" s="1" t="inlineStr">
         <is>
-          <t>L1068: isolated marker/symbol line :: 0</t>
+          <t>L1031: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O336" s="1" t="inlineStr"/>
@@ -13842,7 +13578,7 @@
       <c r="M337" s="1" t="inlineStr"/>
       <c r="N337" s="1" t="inlineStr">
         <is>
-          <t>L1069: isolated marker/symbol line :: "</t>
+          <t>L1032: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O337" s="1" t="inlineStr"/>
@@ -13873,7 +13609,7 @@
       <c r="M338" s="1" t="inlineStr"/>
       <c r="N338" s="1" t="inlineStr">
         <is>
-          <t>L1070: isolated marker/symbol line :: 46</t>
+          <t>L1034: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O338" s="1" t="inlineStr"/>
@@ -13904,7 +13640,7 @@
       <c r="M339" s="1" t="inlineStr"/>
       <c r="N339" s="1" t="inlineStr">
         <is>
-          <t>L1071: isolated marker/symbol line :: 200</t>
+          <t>L1035: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O339" s="1" t="inlineStr"/>
@@ -13935,7 +13671,7 @@
       <c r="M340" s="1" t="inlineStr"/>
       <c r="N340" s="1" t="inlineStr">
         <is>
-          <t>L1072: isolated marker/symbol line :: 2</t>
+          <t>L1053: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O340" s="1" t="inlineStr"/>
@@ -13966,7 +13702,7 @@
       <c r="M341" s="1" t="inlineStr"/>
       <c r="N341" s="1" t="inlineStr">
         <is>
-          <t>L1073: symbol-only separator/garbage line :: 27.</t>
+          <t>L1056: stray/suspicious non-ASCII glyph(s): U+697C CJK UNIFIED IDEOGRAPH-697C | isolated marker/symbol line :: 楼</t>
         </is>
       </c>
       <c r="O341" s="1" t="inlineStr"/>
@@ -13997,7 +13733,7 @@
       <c r="M342" s="1" t="inlineStr"/>
       <c r="N342" s="1" t="inlineStr">
         <is>
-          <t>L1074: isolated marker/symbol line :: 44</t>
+          <t>L1057: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O342" s="1" t="inlineStr"/>
@@ -14028,7 +13764,7 @@
       <c r="M343" s="1" t="inlineStr"/>
       <c r="N343" s="1" t="inlineStr">
         <is>
-          <t>L1075: isolated marker/symbol line :: 46</t>
+          <t>L1060: isolated marker/symbol line :: 19</t>
         </is>
       </c>
       <c r="O343" s="1" t="inlineStr"/>
@@ -14059,7 +13795,7 @@
       <c r="M344" s="1" t="inlineStr"/>
       <c r="N344" s="1" t="inlineStr">
         <is>
-          <t>L1076: isolated marker/symbol line :: "</t>
+          <t>L1061: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O344" s="1" t="inlineStr"/>
@@ -14090,7 +13826,7 @@
       <c r="M345" s="1" t="inlineStr"/>
       <c r="N345" s="1" t="inlineStr">
         <is>
-          <t>L1077: isolated marker/symbol line :: 80</t>
+          <t>L1062: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O345" s="1" t="inlineStr"/>
@@ -14121,7 +13857,7 @@
       <c r="M346" s="1" t="inlineStr"/>
       <c r="N346" s="1" t="inlineStr">
         <is>
-          <t>L1078: isolated marker/symbol line :: 20</t>
+          <t>L1063: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O346" s="1" t="inlineStr"/>
@@ -14152,7 +13888,7 @@
       <c r="M347" s="1" t="inlineStr"/>
       <c r="N347" s="1" t="inlineStr">
         <is>
-          <t>L1079: symbol-only separator/garbage line :: 28.</t>
+          <t>L1064: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O347" s="1" t="inlineStr"/>
@@ -14183,7 +13919,7 @@
       <c r="M348" s="1" t="inlineStr"/>
       <c r="N348" s="1" t="inlineStr">
         <is>
-          <t>L1080: isolated marker/symbol line :: 4</t>
+          <t>L1066: symbol-only separator/garbage line :: 25,</t>
         </is>
       </c>
       <c r="O348" s="1" t="inlineStr"/>
@@ -14214,7 +13950,7 @@
       <c r="M349" s="1" t="inlineStr"/>
       <c r="N349" s="1" t="inlineStr">
         <is>
-          <t>L1081: isolated marker/symbol line :: 200</t>
+          <t>L1067: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O349" s="1" t="inlineStr"/>
@@ -14245,7 +13981,7 @@
       <c r="M350" s="1" t="inlineStr"/>
       <c r="N350" s="1" t="inlineStr">
         <is>
-          <t>L1083: isolated marker/symbol line :: .</t>
+          <t>L1068: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O350" s="1" t="inlineStr"/>
@@ -14276,7 +14012,7 @@
       <c r="M351" s="1" t="inlineStr"/>
       <c r="N351" s="1" t="inlineStr">
         <is>
-          <t>L1084: isolated marker/symbol line :: #</t>
+          <t>L1069: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O351" s="1" t="inlineStr"/>
@@ -14307,7 +14043,7 @@
       <c r="M352" s="1" t="inlineStr"/>
       <c r="N352" s="1" t="inlineStr">
         <is>
-          <t>L1085: isolated marker/symbol line :: 20</t>
+          <t>L1070: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O352" s="1" t="inlineStr"/>
@@ -14338,7 +14074,7 @@
       <c r="M353" s="1" t="inlineStr"/>
       <c r="N353" s="1" t="inlineStr">
         <is>
-          <t>L1086: isolated marker/symbol line :: "</t>
+          <t>L1071: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O353" s="1" t="inlineStr"/>
@@ -14369,7 +14105,7 @@
       <c r="M354" s="1" t="inlineStr"/>
       <c r="N354" s="1" t="inlineStr">
         <is>
-          <t>L1087: isolated marker/symbol line :: $.</t>
+          <t>L1072: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O354" s="1" t="inlineStr"/>
@@ -14400,7 +14136,7 @@
       <c r="M355" s="1" t="inlineStr"/>
       <c r="N355" s="1" t="inlineStr">
         <is>
-          <t>L1088: isolated marker/symbol line :: 200</t>
+          <t>L1073: symbol-only separator/garbage line :: 27.</t>
         </is>
       </c>
       <c r="O355" s="1" t="inlineStr"/>
@@ -14431,7 +14167,7 @@
       <c r="M356" s="1" t="inlineStr"/>
       <c r="N356" s="1" t="inlineStr">
         <is>
-          <t>L1090: isolated marker/symbol line :: 0</t>
+          <t>L1074: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O356" s="1" t="inlineStr"/>
@@ -14462,7 +14198,7 @@
       <c r="M357" s="1" t="inlineStr"/>
       <c r="N357" s="1" t="inlineStr">
         <is>
-          <t>L1091: isolated marker/symbol line :: 200</t>
+          <t>L1075: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O357" s="1" t="inlineStr"/>
@@ -14493,7 +14229,7 @@
       <c r="M358" s="1" t="inlineStr"/>
       <c r="N358" s="1" t="inlineStr">
         <is>
-          <t>L1092: isolated marker/symbol line :: 200</t>
+          <t>L1076: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O358" s="1" t="inlineStr"/>
@@ -14524,7 +14260,7 @@
       <c r="M359" s="1" t="inlineStr"/>
       <c r="N359" s="1" t="inlineStr">
         <is>
-          <t>L1104: isolated marker/symbol line :: 4</t>
+          <t>L1077: isolated marker/symbol line :: 80</t>
         </is>
       </c>
       <c r="O359" s="1" t="inlineStr"/>
@@ -14555,7 +14291,7 @@
       <c r="M360" s="1" t="inlineStr"/>
       <c r="N360" s="1" t="inlineStr">
         <is>
-          <t>L1105: isolated marker/symbol line :: .</t>
+          <t>L1078: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O360" s="1" t="inlineStr"/>
@@ -14586,7 +14322,7 @@
       <c r="M361" s="1" t="inlineStr"/>
       <c r="N361" s="1" t="inlineStr">
         <is>
-          <t>L1106: isolated marker/symbol line :: 4</t>
+          <t>L1079: symbol-only separator/garbage line :: 28.</t>
         </is>
       </c>
       <c r="O361" s="1" t="inlineStr"/>
@@ -14617,7 +14353,7 @@
       <c r="M362" s="1" t="inlineStr"/>
       <c r="N362" s="1" t="inlineStr">
         <is>
-          <t>L1110: isolated marker/symbol line :: 4</t>
+          <t>L1080: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O362" s="1" t="inlineStr"/>
@@ -14648,7 +14384,7 @@
       <c r="M363" s="1" t="inlineStr"/>
       <c r="N363" s="1" t="inlineStr">
         <is>
-          <t>L1118: isolated marker/symbol line :: 1</t>
+          <t>L1081: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O363" s="1" t="inlineStr"/>
@@ -14679,7 +14415,7 @@
       <c r="M364" s="1" t="inlineStr"/>
       <c r="N364" s="1" t="inlineStr">
         <is>
-          <t>L1120: isolated marker/symbol line :: 4</t>
+          <t>L1083: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O364" s="1" t="inlineStr"/>
@@ -14710,7 +14446,7 @@
       <c r="M365" s="1" t="inlineStr"/>
       <c r="N365" s="1" t="inlineStr">
         <is>
-          <t>L1122: isolated marker/symbol line :: 0</t>
+          <t>L1084: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="O365" s="1" t="inlineStr"/>
@@ -14741,7 +14477,7 @@
       <c r="M366" s="1" t="inlineStr"/>
       <c r="N366" s="1" t="inlineStr">
         <is>
-          <t>L1123: isolated marker/symbol line :: S</t>
+          <t>L1085: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O366" s="1" t="inlineStr"/>
@@ -14772,7 +14508,7 @@
       <c r="M367" s="1" t="inlineStr"/>
       <c r="N367" s="1" t="inlineStr">
         <is>
-          <t>L1125: isolated marker/symbol line :: h</t>
+          <t>L1086: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O367" s="1" t="inlineStr"/>
@@ -14803,7 +14539,7 @@
       <c r="M368" s="1" t="inlineStr"/>
       <c r="N368" s="1" t="inlineStr">
         <is>
-          <t>L1126: isolated marker/symbol line :: A</t>
+          <t>L1087: isolated marker/symbol line :: $.</t>
         </is>
       </c>
       <c r="O368" s="1" t="inlineStr"/>
@@ -14834,7 +14570,7 @@
       <c r="M369" s="1" t="inlineStr"/>
       <c r="N369" s="1" t="inlineStr">
         <is>
-          <t>L1129: symbol-only separator/garbage line :: 1860</t>
+          <t>L1088: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O369" s="1" t="inlineStr"/>
@@ -14865,7 +14601,7 @@
       <c r="M370" s="1" t="inlineStr"/>
       <c r="N370" s="1" t="inlineStr">
         <is>
-          <t>L1130: isolated marker/symbol line :: 4</t>
+          <t>L1090: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O370" s="1" t="inlineStr"/>
@@ -14896,7 +14632,7 @@
       <c r="M371" s="1" t="inlineStr"/>
       <c r="N371" s="1" t="inlineStr">
         <is>
-          <t>L1132: symbol-only separator/garbage line :: 8.25</t>
+          <t>L1091: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O371" s="1" t="inlineStr"/>
@@ -14927,7 +14663,7 @@
       <c r="M372" s="1" t="inlineStr"/>
       <c r="N372" s="1" t="inlineStr">
         <is>
-          <t>L1134: isolated marker/symbol line :: 531</t>
+          <t>L1092: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O372" s="1" t="inlineStr"/>
@@ -14958,7 +14694,7 @@
       <c r="M373" s="1" t="inlineStr"/>
       <c r="N373" s="1" t="inlineStr">
         <is>
-          <t>L1137: symbol-only separator/garbage line :: 7, 13</t>
+          <t>L1104: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O373" s="1" t="inlineStr"/>
@@ -14989,7 +14725,7 @@
       <c r="M374" s="1" t="inlineStr"/>
       <c r="N374" s="1" t="inlineStr">
         <is>
-          <t>L1138: symbol-only separator/garbage line :: 3, 13</t>
+          <t>L1105: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O374" s="1" t="inlineStr"/>
@@ -15020,7 +14756,7 @@
       <c r="M375" s="1" t="inlineStr"/>
       <c r="N375" s="1" t="inlineStr">
         <is>
-          <t>L1142: symbol-only separator/garbage line :: 10.80</t>
+          <t>L1106: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O375" s="1" t="inlineStr"/>
@@ -15051,7 +14787,7 @@
       <c r="M376" s="1" t="inlineStr"/>
       <c r="N376" s="1" t="inlineStr">
         <is>
-          <t>L1144: isolated marker/symbol line :: 2</t>
+          <t>L1109: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O376" s="1" t="inlineStr"/>
@@ -15082,7 +14818,7 @@
       <c r="M377" s="1" t="inlineStr"/>
       <c r="N377" s="1" t="inlineStr">
         <is>
-          <t>L1145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+2122 TRADE MARK SIGN | isolated marker/symbol line :: æ•™</t>
+          <t>L1110: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O377" s="1" t="inlineStr"/>
@@ -15113,7 +14849,7 @@
       <c r="M378" s="1" t="inlineStr"/>
       <c r="N378" s="1" t="inlineStr">
         <is>
-          <t>L1147: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1111: stray/suspicious non-ASCII glyph(s): U+4E8B CJK UNIFIED IDEOGRAPH-4E8B | isolated marker/symbol line :: 事</t>
         </is>
       </c>
       <c r="O378" s="1" t="inlineStr"/>
@@ -15144,7 +14880,7 @@
       <c r="M379" s="1" t="inlineStr"/>
       <c r="N379" s="1" t="inlineStr">
         <is>
-          <t>L1149: symbol-only separator/garbage line :: 7.80</t>
+          <t>L1112: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O379" s="1" t="inlineStr"/>
@@ -15175,7 +14911,7 @@
       <c r="M380" s="1" t="inlineStr"/>
       <c r="N380" s="1" t="inlineStr">
         <is>
-          <t>L1151: isolated marker/symbol line :: D</t>
+          <t>L1118: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O380" s="1" t="inlineStr"/>
@@ -15206,7 +14942,7 @@
       <c r="M381" s="1" t="inlineStr"/>
       <c r="N381" s="1" t="inlineStr">
         <is>
-          <t>L1153: symbol-only separator/garbage line :: 20.00</t>
+          <t>L1120: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O381" s="1" t="inlineStr"/>
@@ -15237,7 +14973,7 @@
       <c r="M382" s="1" t="inlineStr"/>
       <c r="N382" s="1" t="inlineStr">
         <is>
-          <t>L1155: symbol-only separator/garbage line :: 5.60</t>
+          <t>L1121: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O382" s="1" t="inlineStr"/>
@@ -15268,7 +15004,7 @@
       <c r="M383" s="1" t="inlineStr"/>
       <c r="N383" s="1" t="inlineStr">
         <is>
-          <t>L1157: isolated marker/symbol line :: 250</t>
+          <t>L1122: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O383" s="1" t="inlineStr"/>
@@ -15299,7 +15035,7 @@
       <c r="M384" s="1" t="inlineStr"/>
       <c r="N384" s="1" t="inlineStr">
         <is>
-          <t>L1159: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1123: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O384" s="1" t="inlineStr"/>
@@ -15330,7 +15066,7 @@
       <c r="M385" s="1" t="inlineStr"/>
       <c r="N385" s="1" t="inlineStr">
         <is>
-          <t>L1161: isolated marker/symbol line :: 8</t>
+          <t>L1125: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="O385" s="1" t="inlineStr"/>
@@ -15361,7 +15097,7 @@
       <c r="M386" s="1" t="inlineStr"/>
       <c r="N386" s="1" t="inlineStr">
         <is>
-          <t>L1162: symbol-only separator/garbage line :: 1.12</t>
+          <t>L1126: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O386" s="1" t="inlineStr"/>
@@ -15392,7 +15128,7 @@
       <c r="M387" s="1" t="inlineStr"/>
       <c r="N387" s="1" t="inlineStr">
         <is>
-          <t>L1165: symbol-only separator/garbage line :: 11.2</t>
+          <t>L1129: symbol-only separator/garbage line :: 1860</t>
         </is>
       </c>
       <c r="O387" s="1" t="inlineStr"/>
@@ -15423,7 +15159,7 @@
       <c r="M388" s="1" t="inlineStr"/>
       <c r="N388" s="1" t="inlineStr">
         <is>
-          <t>L1166: symbol-only separator/garbage line :: 11.3</t>
+          <t>L1130: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O388" s="1" t="inlineStr"/>
@@ -15454,7 +15190,7 @@
       <c r="M389" s="1" t="inlineStr"/>
       <c r="N389" s="1" t="inlineStr">
         <is>
-          <t>L1168: isolated marker/symbol line :: 451</t>
+          <t>L1132: symbol-only separator/garbage line :: 8.25</t>
         </is>
       </c>
       <c r="O389" s="1" t="inlineStr"/>
@@ -15485,7 +15221,7 @@
       <c r="M390" s="1" t="inlineStr"/>
       <c r="N390" s="1" t="inlineStr">
         <is>
-          <t>L1170: isolated marker/symbol line :: 12</t>
+          <t>L1134: isolated marker/symbol line :: 531</t>
         </is>
       </c>
       <c r="O390" s="1" t="inlineStr"/>
@@ -15516,7 +15252,7 @@
       <c r="M391" s="1" t="inlineStr"/>
       <c r="N391" s="1" t="inlineStr">
         <is>
-          <t>L1173: symbol-only separator/garbage line :: 7.10</t>
+          <t>L1137: symbol-only separator/garbage line :: 7, 13</t>
         </is>
       </c>
       <c r="O391" s="1" t="inlineStr"/>
@@ -15547,7 +15283,7 @@
       <c r="M392" s="1" t="inlineStr"/>
       <c r="N392" s="1" t="inlineStr">
         <is>
-          <t>L1175: isolated marker/symbol line :: .</t>
+          <t>L1138: symbol-only separator/garbage line :: 3, 13</t>
         </is>
       </c>
       <c r="O392" s="1" t="inlineStr"/>
@@ -15578,7 +15314,7 @@
       <c r="M393" s="1" t="inlineStr"/>
       <c r="N393" s="1" t="inlineStr">
         <is>
-          <t>L1177: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1142: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O393" s="1" t="inlineStr"/>
@@ -15609,7 +15345,7 @@
       <c r="M394" s="1" t="inlineStr"/>
       <c r="N394" s="1" t="inlineStr">
         <is>
-          <t>L1179: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L1144: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O394" s="1" t="inlineStr"/>
@@ -15640,7 +15376,7 @@
       <c r="M395" s="1" t="inlineStr"/>
       <c r="N395" s="1" t="inlineStr">
         <is>
-          <t>L1181: symbol-only separator/garbage line :: $116, 374</t>
+          <t>L1145: stray/suspicious non-ASCII glyph(s): U+6559 CJK UNIFIED IDEOGRAPH-6559 | isolated marker/symbol line :: 教</t>
         </is>
       </c>
       <c r="O395" s="1" t="inlineStr"/>
@@ -15671,7 +15407,7 @@
       <c r="M396" s="1" t="inlineStr"/>
       <c r="N396" s="1" t="inlineStr">
         <is>
-          <t>L1183: isolated marker/symbol line :: 100</t>
+          <t>L1147: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O396" s="1" t="inlineStr"/>
@@ -15702,7 +15438,7 @@
       <c r="M397" s="1" t="inlineStr"/>
       <c r="N397" s="1" t="inlineStr">
         <is>
-          <t>L1185: isolated marker/symbol line :: 6</t>
+          <t>L1149: symbol-only separator/garbage line :: 7.80</t>
         </is>
       </c>
       <c r="O397" s="1" t="inlineStr"/>
@@ -15733,7 +15469,7 @@
       <c r="M398" s="1" t="inlineStr"/>
       <c r="N398" s="1" t="inlineStr">
         <is>
-          <t>L1186: isolated marker/symbol line :: 65</t>
+          <t>L1151: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O398" s="1" t="inlineStr"/>
@@ -15764,7 +15500,7 @@
       <c r="M399" s="1" t="inlineStr"/>
       <c r="N399" s="1" t="inlineStr">
         <is>
-          <t>L1187: isolated marker/symbol line :: 2</t>
+          <t>L1153: symbol-only separator/garbage line :: 20.00</t>
         </is>
       </c>
       <c r="O399" s="1" t="inlineStr"/>
@@ -15795,7 +15531,7 @@
       <c r="M400" s="1" t="inlineStr"/>
       <c r="N400" s="1" t="inlineStr">
         <is>
-          <t>L1190: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L1155: symbol-only separator/garbage line :: 5.60</t>
         </is>
       </c>
       <c r="O400" s="1" t="inlineStr"/>
@@ -15826,7 +15562,7 @@
       <c r="M401" s="1" t="inlineStr"/>
       <c r="N401" s="1" t="inlineStr">
         <is>
-          <t>L1194: isolated marker/symbol line :: .</t>
+          <t>L1157: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O401" s="1" t="inlineStr"/>
@@ -15857,7 +15593,7 @@
       <c r="M402" s="1" t="inlineStr"/>
       <c r="N402" s="1" t="inlineStr">
         <is>
-          <t>L1195: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L1159: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O402" s="1" t="inlineStr"/>
@@ -15888,7 +15624,7 @@
       <c r="M403" s="1" t="inlineStr"/>
       <c r="N403" s="1" t="inlineStr">
         <is>
-          <t>L1196: isolated marker/symbol line :: '</t>
+          <t>L1161: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O403" s="1" t="inlineStr"/>
@@ -15919,7 +15655,7 @@
       <c r="M404" s="1" t="inlineStr"/>
       <c r="N404" s="1" t="inlineStr">
         <is>
-          <t>L1197: isolated marker/symbol line :: .</t>
+          <t>L1162: symbol-only separator/garbage line :: 1.12</t>
         </is>
       </c>
       <c r="O404" s="1" t="inlineStr"/>
@@ -15950,7 +15686,7 @@
       <c r="M405" s="1" t="inlineStr"/>
       <c r="N405" s="1" t="inlineStr">
         <is>
-          <t>L1199: isolated marker/symbol line :: 0</t>
+          <t>L1165: symbol-only separator/garbage line :: 11.2</t>
         </is>
       </c>
       <c r="O405" s="1" t="inlineStr"/>
@@ -15981,7 +15717,7 @@
       <c r="M406" s="1" t="inlineStr"/>
       <c r="N406" s="1" t="inlineStr">
         <is>
-          <t>L1201: isolated marker/symbol line :: 1</t>
+          <t>L1166: symbol-only separator/garbage line :: 11.3</t>
         </is>
       </c>
       <c r="O406" s="1" t="inlineStr"/>
@@ -16012,7 +15748,7 @@
       <c r="M407" s="1" t="inlineStr"/>
       <c r="N407" s="1" t="inlineStr">
         <is>
-          <t>L1203: symbol-only separator/garbage line :: 12, 90</t>
+          <t>L1168: isolated marker/symbol line :: 451</t>
         </is>
       </c>
       <c r="O407" s="1" t="inlineStr"/>
@@ -16043,7 +15779,7 @@
       <c r="M408" s="1" t="inlineStr"/>
       <c r="N408" s="1" t="inlineStr">
         <is>
-          <t>L1206: isolated marker/symbol line :: d</t>
+          <t>L1170: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O408" s="1" t="inlineStr"/>
@@ -16074,7 +15810,7 @@
       <c r="M409" s="1" t="inlineStr"/>
       <c r="N409" s="1" t="inlineStr">
         <is>
-          <t>L1210: symbol-only separator/garbage line :: 220.00</t>
+          <t>L1173: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O409" s="1" t="inlineStr"/>
@@ -16105,7 +15841,7 @@
       <c r="M410" s="1" t="inlineStr"/>
       <c r="N410" s="1" t="inlineStr">
         <is>
-          <t>L1212: symbol-only separator/garbage line :: 6, 00</t>
+          <t>L1175: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O410" s="1" t="inlineStr"/>
@@ -16136,7 +15872,7 @@
       <c r="M411" s="1" t="inlineStr"/>
       <c r="N411" s="1" t="inlineStr">
         <is>
-          <t>L1214: isolated marker/symbol line :: 3</t>
+          <t>L1177: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O411" s="1" t="inlineStr"/>
@@ -16167,7 +15903,7 @@
       <c r="M412" s="1" t="inlineStr"/>
       <c r="N412" s="1" t="inlineStr">
         <is>
-          <t>L1216: symbol-only separator/garbage line :: 3.00</t>
+          <t>L1179: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O412" s="1" t="inlineStr"/>
@@ -16198,7 +15934,7 @@
       <c r="M413" s="1" t="inlineStr"/>
       <c r="N413" s="1" t="inlineStr">
         <is>
-          <t>L1218: symbol-only separator/garbage line :: 7.55</t>
+          <t>L1181: symbol-only separator/garbage line :: $116, 374</t>
         </is>
       </c>
       <c r="O413" s="1" t="inlineStr"/>
@@ -16229,7 +15965,7 @@
       <c r="M414" s="1" t="inlineStr"/>
       <c r="N414" s="1" t="inlineStr">
         <is>
-          <t>L1220: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1183: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O414" s="1" t="inlineStr"/>
@@ -16260,7 +15996,7 @@
       <c r="M415" s="1" t="inlineStr"/>
       <c r="N415" s="1" t="inlineStr">
         <is>
-          <t>L1222: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L1185: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O415" s="1" t="inlineStr"/>
@@ -16291,7 +16027,7 @@
       <c r="M416" s="1" t="inlineStr"/>
       <c r="N416" s="1" t="inlineStr">
         <is>
-          <t>L1225: isolated marker/symbol line :: 20</t>
+          <t>L1186: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O416" s="1" t="inlineStr"/>
@@ -16322,7 +16058,7 @@
       <c r="M417" s="1" t="inlineStr"/>
       <c r="N417" s="1" t="inlineStr">
         <is>
-          <t>L1226: isolated marker/symbol line :: 3</t>
+          <t>L1187: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O417" s="1" t="inlineStr"/>
@@ -16353,7 +16089,7 @@
       <c r="M418" s="1" t="inlineStr"/>
       <c r="N418" s="1" t="inlineStr">
         <is>
-          <t>L1231: isolated marker/symbol line :: 8</t>
+          <t>L1190: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O418" s="1" t="inlineStr"/>
@@ -16384,7 +16120,7 @@
       <c r="M419" s="1" t="inlineStr"/>
       <c r="N419" s="1" t="inlineStr">
         <is>
-          <t>L1235: isolated marker/symbol line :: M</t>
+          <t>L1194: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O419" s="1" t="inlineStr"/>
@@ -16415,7 +16151,7 @@
       <c r="M420" s="1" t="inlineStr"/>
       <c r="N420" s="1" t="inlineStr">
         <is>
-          <t>L1236: isolated marker/symbol line :: 0</t>
+          <t>L1195: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O420" s="1" t="inlineStr"/>
@@ -16446,7 +16182,7 @@
       <c r="M421" s="1" t="inlineStr"/>
       <c r="N421" s="1" t="inlineStr">
         <is>
-          <t>L1242: symbol-only separator/garbage line :: 618.60</t>
+          <t>L1196: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O421" s="1" t="inlineStr"/>
@@ -16477,7 +16213,7 @@
       <c r="M422" s="1" t="inlineStr"/>
       <c r="N422" s="1" t="inlineStr">
         <is>
-          <t>L1246: symbol-only separator/garbage line :: 182.25</t>
+          <t>L1197: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O422" s="1" t="inlineStr"/>
@@ -16508,7 +16244,7 @@
       <c r="M423" s="1" t="inlineStr"/>
       <c r="N423" s="1" t="inlineStr">
         <is>
-          <t>L1249: isolated marker/symbol line :: X</t>
+          <t>L1199: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O423" s="1" t="inlineStr"/>
@@ -16539,7 +16275,7 @@
       <c r="M424" s="1" t="inlineStr"/>
       <c r="N424" s="1" t="inlineStr">
         <is>
-          <t>L1251: symbol-only separator/garbage line :: 114.00</t>
+          <t>L1201: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O424" s="1" t="inlineStr"/>
@@ -16570,7 +16306,7 @@
       <c r="M425" s="1" t="inlineStr"/>
       <c r="N425" s="1" t="inlineStr">
         <is>
-          <t>L1254: symbol-only separator/garbage line :: 54.00</t>
+          <t>L1203: symbol-only separator/garbage line :: 12, 90</t>
         </is>
       </c>
       <c r="O425" s="1" t="inlineStr"/>
@@ -16601,7 +16337,7 @@
       <c r="M426" s="1" t="inlineStr"/>
       <c r="N426" s="1" t="inlineStr">
         <is>
-          <t>L1257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L1206: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O426" s="1" t="inlineStr"/>
@@ -16632,7 +16368,7 @@
       <c r="M427" s="1" t="inlineStr"/>
       <c r="N427" s="1" t="inlineStr">
         <is>
-          <t>L1258: symbol-only separator/garbage line :: 1.39</t>
+          <t>L1210: symbol-only separator/garbage line :: 220.00</t>
         </is>
       </c>
       <c r="O427" s="1" t="inlineStr"/>
@@ -16663,7 +16399,7 @@
       <c r="M428" s="1" t="inlineStr"/>
       <c r="N428" s="1" t="inlineStr">
         <is>
-          <t>L1260: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å”®</t>
+          <t>L1212: symbol-only separator/garbage line :: 6, 00</t>
         </is>
       </c>
       <c r="O428" s="1" t="inlineStr"/>
@@ -16694,7 +16430,7 @@
       <c r="M429" s="1" t="inlineStr"/>
       <c r="N429" s="1" t="inlineStr">
         <is>
-          <t>L1262: isolated marker/symbol line :: &amp;</t>
+          <t>L1214: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O429" s="1" t="inlineStr"/>
@@ -16725,7 +16461,7 @@
       <c r="M430" s="1" t="inlineStr"/>
       <c r="N430" s="1" t="inlineStr">
         <is>
-          <t>L1263: isolated marker/symbol line :: 240</t>
+          <t>L1216: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O430" s="1" t="inlineStr"/>
@@ -16756,7 +16492,7 @@
       <c r="M431" s="1" t="inlineStr"/>
       <c r="N431" s="1" t="inlineStr">
         <is>
-          <t>L1265: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L1218: symbol-only separator/garbage line :: 7.55</t>
         </is>
       </c>
       <c r="O431" s="1" t="inlineStr"/>
@@ -16787,7 +16523,7 @@
       <c r="M432" s="1" t="inlineStr"/>
       <c r="N432" s="1" t="inlineStr">
         <is>
-          <t>L1280: symbol-only separator/garbage line :: 523, 75</t>
+          <t>L1220: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O432" s="1" t="inlineStr"/>
@@ -16818,7 +16554,7 @@
       <c r="M433" s="1" t="inlineStr"/>
       <c r="N433" s="1" t="inlineStr">
         <is>
-          <t>L1282: symbol-only separator/garbage line :: 1016, 00</t>
+          <t>L1222: symbol-only separator/garbage line :: 9, 16</t>
         </is>
       </c>
       <c r="O433" s="1" t="inlineStr"/>
@@ -16849,7 +16585,7 @@
       <c r="M434" s="1" t="inlineStr"/>
       <c r="N434" s="1" t="inlineStr">
         <is>
-          <t>L1286: symbol-only separator/garbage line :: 167, 65</t>
+          <t>L1225: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O434" s="1" t="inlineStr"/>
@@ -16880,7 +16616,7 @@
       <c r="M435" s="1" t="inlineStr"/>
       <c r="N435" s="1" t="inlineStr">
         <is>
-          <t>L1288: isolated marker/symbol line :: 4</t>
+          <t>L1226: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O435" s="1" t="inlineStr"/>
@@ -16911,7 +16647,7 @@
       <c r="M436" s="1" t="inlineStr"/>
       <c r="N436" s="1" t="inlineStr">
         <is>
-          <t>L1289: isolated marker/symbol line :: m</t>
+          <t>L1230: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。。</t>
         </is>
       </c>
       <c r="O436" s="1" t="inlineStr"/>
@@ -16942,7 +16678,7 @@
       <c r="M437" s="1" t="inlineStr"/>
       <c r="N437" s="1" t="inlineStr">
         <is>
-          <t>L1290: isolated marker/symbol line :: 2</t>
+          <t>L1231: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O437" s="1" t="inlineStr"/>
@@ -16973,7 +16709,7 @@
       <c r="M438" s="1" t="inlineStr"/>
       <c r="N438" s="1" t="inlineStr">
         <is>
-          <t>L1293: symbol-only separator/garbage line :: 34.48</t>
+          <t>L1235: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O438" s="1" t="inlineStr"/>
@@ -17004,7 +16740,7 @@
       <c r="M439" s="1" t="inlineStr"/>
       <c r="N439" s="1" t="inlineStr">
         <is>
-          <t>L1294: isolated marker/symbol line :: é›…</t>
+          <t>L1236: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O439" s="1" t="inlineStr"/>
@@ -17035,7 +16771,7 @@
       <c r="M440" s="1" t="inlineStr"/>
       <c r="N440" s="1" t="inlineStr">
         <is>
-          <t>L1296: symbol-only separator/garbage line :: 15, 13</t>
+          <t>L1242: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="O440" s="1" t="inlineStr"/>
@@ -17066,7 +16802,7 @@
       <c r="M441" s="1" t="inlineStr"/>
       <c r="N441" s="1" t="inlineStr">
         <is>
-          <t>L1298: isolated marker/symbol line :: ,</t>
+          <t>L1246: symbol-only separator/garbage line :: 182.25</t>
         </is>
       </c>
       <c r="O441" s="1" t="inlineStr"/>
@@ -17097,7 +16833,7 @@
       <c r="M442" s="1" t="inlineStr"/>
       <c r="N442" s="1" t="inlineStr">
         <is>
-          <t>L1300: symbol-only separator/garbage line :: 23.25</t>
+          <t>L1249: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O442" s="1" t="inlineStr"/>
@@ -17128,7 +16864,7 @@
       <c r="M443" s="1" t="inlineStr"/>
       <c r="N443" s="1" t="inlineStr">
         <is>
-          <t>L1303: symbol-only separator/garbage line :: 12.70</t>
+          <t>L1251: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="O443" s="1" t="inlineStr"/>
@@ -17159,7 +16895,7 @@
       <c r="M444" s="1" t="inlineStr"/>
       <c r="N444" s="1" t="inlineStr">
         <is>
-          <t>L1305: symbol-only separator/garbage line :: 1130</t>
+          <t>L1254: symbol-only separator/garbage line :: 54.00</t>
         </is>
       </c>
       <c r="O444" s="1" t="inlineStr"/>
@@ -17190,7 +16926,7 @@
       <c r="M445" s="1" t="inlineStr"/>
       <c r="N445" s="1" t="inlineStr">
         <is>
-          <t>L1307: symbol-only separator/garbage line :: 7.72</t>
+          <t>L1257: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O445" s="1" t="inlineStr"/>
@@ -17221,7 +16957,7 @@
       <c r="M446" s="1" t="inlineStr"/>
       <c r="N446" s="1" t="inlineStr">
         <is>
-          <t>L1309: symbol-only separator/garbage line :: 140.0</t>
+          <t>L1258: symbol-only separator/garbage line :: 1.39</t>
         </is>
       </c>
       <c r="O446" s="1" t="inlineStr"/>
@@ -17252,7 +16988,7 @@
       <c r="M447" s="1" t="inlineStr"/>
       <c r="N447" s="1" t="inlineStr">
         <is>
-          <t>L1311: isolated marker/symbol line :: 1</t>
+          <t>L1260: stray/suspicious non-ASCII glyph(s): U+552E CJK UNIFIED IDEOGRAPH-552E | isolated marker/symbol line :: 售</t>
         </is>
       </c>
       <c r="O447" s="1" t="inlineStr"/>
@@ -17283,7 +17019,7 @@
       <c r="M448" s="1" t="inlineStr"/>
       <c r="N448" s="1" t="inlineStr">
         <is>
-          <t>L1312: symbol-only separator/garbage line :: 4.20</t>
+          <t>L1262: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O448" s="1" t="inlineStr"/>
@@ -17314,7 +17050,7 @@
       <c r="M449" s="1" t="inlineStr"/>
       <c r="N449" s="1" t="inlineStr">
         <is>
-          <t>L1316: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1263: isolated marker/symbol line :: 240</t>
         </is>
       </c>
       <c r="O449" s="1" t="inlineStr"/>
@@ -17345,7 +17081,7 @@
       <c r="M450" s="1" t="inlineStr"/>
       <c r="N450" s="1" t="inlineStr">
         <is>
-          <t>L1318: isolated marker/symbol line :: 1</t>
+          <t>L1264: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: c −</t>
         </is>
       </c>
       <c r="O450" s="1" t="inlineStr"/>
@@ -17376,7 +17112,7 @@
       <c r="M451" s="1" t="inlineStr"/>
       <c r="N451" s="1" t="inlineStr">
         <is>
-          <t>L1319: symbol-only separator/garbage line :: 2.85</t>
+          <t>L1265: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="O451" s="1" t="inlineStr"/>
@@ -17407,7 +17143,7 @@
       <c r="M452" s="1" t="inlineStr"/>
       <c r="N452" s="1" t="inlineStr">
         <is>
-          <t>L1321: symbol-only separator/garbage line :: 8515</t>
+          <t>L1280: symbol-only separator/garbage line :: 523, 75</t>
         </is>
       </c>
       <c r="O452" s="1" t="inlineStr"/>
@@ -17438,7 +17174,7 @@
       <c r="M453" s="1" t="inlineStr"/>
       <c r="N453" s="1" t="inlineStr">
         <is>
-          <t>L1324: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L1282: symbol-only separator/garbage line :: 1016, 00</t>
         </is>
       </c>
       <c r="O453" s="1" t="inlineStr"/>
@@ -17469,7 +17205,7 @@
       <c r="M454" s="1" t="inlineStr"/>
       <c r="N454" s="1" t="inlineStr">
         <is>
-          <t>L1325: symbol-only separator/garbage line :: 9.60</t>
+          <t>L1286: symbol-only separator/garbage line :: 167, 65</t>
         </is>
       </c>
       <c r="O454" s="1" t="inlineStr"/>
@@ -17500,7 +17236,7 @@
       <c r="M455" s="1" t="inlineStr"/>
       <c r="N455" s="1" t="inlineStr">
         <is>
-          <t>L1326: symbol-only separator/garbage line :: 9.61</t>
+          <t>L1288: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O455" s="1" t="inlineStr"/>
@@ -17531,7 +17267,7 @@
       <c r="M456" s="1" t="inlineStr"/>
       <c r="N456" s="1" t="inlineStr">
         <is>
-          <t>L1328: symbol-only separator/garbage line :: 53.80</t>
+          <t>L1289: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O456" s="1" t="inlineStr"/>
@@ -17562,7 +17298,7 @@
       <c r="M457" s="1" t="inlineStr"/>
       <c r="N457" s="1" t="inlineStr">
         <is>
-          <t>L1332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L1290: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O457" s="1" t="inlineStr"/>
@@ -17593,7 +17329,7 @@
       <c r="M458" s="1" t="inlineStr"/>
       <c r="N458" s="1" t="inlineStr">
         <is>
-          <t>L1333: symbol-only separator/garbage line :: 6167</t>
+          <t>L1291: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
         </is>
       </c>
       <c r="O458" s="1" t="inlineStr"/>
@@ -17624,7 +17360,7 @@
       <c r="M459" s="1" t="inlineStr"/>
       <c r="N459" s="1" t="inlineStr">
         <is>
-          <t>L1350: isolated marker/symbol line :: e.</t>
+          <t>L1293: symbol-only separator/garbage line :: 34.48</t>
         </is>
       </c>
       <c r="O459" s="1" t="inlineStr"/>
@@ -17655,7 +17391,7 @@
       <c r="M460" s="1" t="inlineStr"/>
       <c r="N460" s="1" t="inlineStr">
         <is>
-          <t>L1378: symbol-only separator/garbage line :: 618, 60</t>
+          <t>L1294: stray/suspicious non-ASCII glyph(s): U+96C5 CJK UNIFIED IDEOGRAPH-96C5 | isolated marker/symbol line :: 雅</t>
         </is>
       </c>
       <c r="O460" s="1" t="inlineStr"/>
@@ -17686,7 +17422,7 @@
       <c r="M461" s="1" t="inlineStr"/>
       <c r="N461" s="1" t="inlineStr">
         <is>
-          <t>L1382: isolated marker/symbol line :: 0</t>
+          <t>L1296: symbol-only separator/garbage line :: 15, 13</t>
         </is>
       </c>
       <c r="O461" s="1" t="inlineStr"/>
@@ -17717,7 +17453,7 @@
       <c r="M462" s="1" t="inlineStr"/>
       <c r="N462" s="1" t="inlineStr">
         <is>
-          <t>L1388: isolated marker/symbol line :: c</t>
+          <t>L1298: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O462" s="1" t="inlineStr"/>
@@ -17748,7 +17484,7 @@
       <c r="M463" s="1" t="inlineStr"/>
       <c r="N463" s="1" t="inlineStr">
         <is>
-          <t>L1401: isolated marker/symbol line :: i</t>
+          <t>L1300: symbol-only separator/garbage line :: 23.25</t>
         </is>
       </c>
       <c r="O463" s="1" t="inlineStr"/>
@@ -17779,7 +17515,7 @@
       <c r="M464" s="1" t="inlineStr"/>
       <c r="N464" s="1" t="inlineStr">
         <is>
-          <t>L1418: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ä¿�</t>
+          <t>L1301: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O464" s="1" t="inlineStr"/>
@@ -17810,7 +17546,7 @@
       <c r="M465" s="1" t="inlineStr"/>
       <c r="N465" s="1" t="inlineStr">
         <is>
-          <t>L1419: isolated marker/symbol line :: %</t>
+          <t>L1303: symbol-only separator/garbage line :: 12.70</t>
         </is>
       </c>
       <c r="O465" s="1" t="inlineStr"/>
@@ -17841,7 +17577,7 @@
       <c r="M466" s="1" t="inlineStr"/>
       <c r="N466" s="1" t="inlineStr">
         <is>
-          <t>L1428: isolated marker/symbol line :: "</t>
+          <t>L1305: symbol-only separator/garbage line :: 1130</t>
         </is>
       </c>
       <c r="O466" s="1" t="inlineStr"/>
@@ -17872,7 +17608,7 @@
       <c r="M467" s="1" t="inlineStr"/>
       <c r="N467" s="1" t="inlineStr">
         <is>
-          <t>L1429: isolated marker/symbol line :: 7</t>
+          <t>L1307: symbol-only separator/garbage line :: 7.72</t>
         </is>
       </c>
       <c r="O467" s="1" t="inlineStr"/>
@@ -17903,7 +17639,7 @@
       <c r="M468" s="1" t="inlineStr"/>
       <c r="N468" s="1" t="inlineStr">
         <is>
-          <t>L1430: isolated marker/symbol line :: A</t>
+          <t>L1309: symbol-only separator/garbage line :: 140.0</t>
         </is>
       </c>
       <c r="O468" s="1" t="inlineStr"/>
@@ -17934,7 +17670,7 @@
       <c r="M469" s="1" t="inlineStr"/>
       <c r="N469" s="1" t="inlineStr">
         <is>
-          <t>L1432: isolated marker/symbol line :: X</t>
+          <t>L1311: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O469" s="1" t="inlineStr"/>
@@ -17965,7 +17701,7 @@
       <c r="M470" s="1" t="inlineStr"/>
       <c r="N470" s="1" t="inlineStr">
         <is>
-          <t>L1433: isolated marker/symbol line :: æ°”</t>
+          <t>L1312: symbol-only separator/garbage line :: 4.20</t>
         </is>
       </c>
       <c r="O470" s="1" t="inlineStr"/>
@@ -17996,7 +17732,7 @@
       <c r="M471" s="1" t="inlineStr"/>
       <c r="N471" s="1" t="inlineStr">
         <is>
-          <t>L1434: symbol-only separator/garbage line :: $2760.20</t>
+          <t>L1316: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O471" s="1" t="inlineStr"/>
@@ -18027,7 +17763,7 @@
       <c r="M472" s="1" t="inlineStr"/>
       <c r="N472" s="1" t="inlineStr">
         <is>
-          <t>L1436: isolated marker/symbol line :: 1</t>
+          <t>L1318: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O472" s="1" t="inlineStr"/>
@@ -18058,7 +17794,7 @@
       <c r="M473" s="1" t="inlineStr"/>
       <c r="N473" s="1" t="inlineStr">
         <is>
-          <t>L1437: isolated marker/symbol line :: .</t>
+          <t>L1319: symbol-only separator/garbage line :: 2.85</t>
         </is>
       </c>
       <c r="O473" s="1" t="inlineStr"/>
@@ -18089,7 +17825,7 @@
       <c r="M474" s="1" t="inlineStr"/>
       <c r="N474" s="1" t="inlineStr">
         <is>
-          <t>L1459: isolated marker/symbol line :: 2</t>
+          <t>L1321: symbol-only separator/garbage line :: 8515</t>
         </is>
       </c>
       <c r="O474" s="1" t="inlineStr"/>
@@ -18120,7 +17856,7 @@
       <c r="M475" s="1" t="inlineStr"/>
       <c r="N475" s="1" t="inlineStr">
         <is>
-          <t>L1467: isolated marker/symbol line :: i</t>
+          <t>L1324: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O475" s="1" t="inlineStr"/>
@@ -18151,7 +17887,7 @@
       <c r="M476" s="1" t="inlineStr"/>
       <c r="N476" s="1" t="inlineStr">
         <is>
-          <t>L1478: isolated marker/symbol line :: -</t>
+          <t>L1325: symbol-only separator/garbage line :: 9.60</t>
         </is>
       </c>
       <c r="O476" s="1" t="inlineStr"/>
@@ -18182,7 +17918,7 @@
       <c r="M477" s="1" t="inlineStr"/>
       <c r="N477" s="1" t="inlineStr">
         <is>
-          <t>L1481: isolated marker/symbol line :: W $</t>
+          <t>L1326: symbol-only separator/garbage line :: 9.61</t>
         </is>
       </c>
       <c r="O477" s="1" t="inlineStr"/>
@@ -18213,7 +17949,7 @@
       <c r="M478" s="1" t="inlineStr"/>
       <c r="N478" s="1" t="inlineStr">
         <is>
-          <t>L1486: isolated marker/symbol line :: 5</t>
+          <t>L1328: symbol-only separator/garbage line :: 53.80</t>
         </is>
       </c>
       <c r="O478" s="1" t="inlineStr"/>
@@ -18244,7 +17980,7 @@
       <c r="M479" s="1" t="inlineStr"/>
       <c r="N479" s="1" t="inlineStr">
         <is>
-          <t>L1524: isolated marker/symbol line :: 1</t>
+          <t>L1332: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O479" s="1" t="inlineStr"/>
@@ -18275,7 +18011,7 @@
       <c r="M480" s="1" t="inlineStr"/>
       <c r="N480" s="1" t="inlineStr">
         <is>
-          <t>L1529: isolated marker/symbol line :: -</t>
+          <t>L1333: symbol-only separator/garbage line :: 6167</t>
         </is>
       </c>
       <c r="O480" s="1" t="inlineStr"/>
@@ -18306,7 +18042,7 @@
       <c r="M481" s="1" t="inlineStr"/>
       <c r="N481" s="1" t="inlineStr">
         <is>
-          <t>L1531: isolated marker/symbol line :: 0</t>
+          <t>L1350: isolated marker/symbol line :: e.</t>
         </is>
       </c>
       <c r="O481" s="1" t="inlineStr"/>
@@ -18337,7 +18073,7 @@
       <c r="M482" s="1" t="inlineStr"/>
       <c r="N482" s="1" t="inlineStr">
         <is>
-          <t>L1561: isolated marker/symbol line :: 8</t>
+          <t>L1378: symbol-only separator/garbage line :: 618, 60</t>
         </is>
       </c>
       <c r="O482" s="1" t="inlineStr"/>
@@ -18368,7 +18104,7 @@
       <c r="M483" s="1" t="inlineStr"/>
       <c r="N483" s="1" t="inlineStr">
         <is>
-          <t>L1569: isolated marker/symbol line :: é“¶</t>
+          <t>L1382: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O483" s="1" t="inlineStr"/>
@@ -18399,7 +18135,7 @@
       <c r="M484" s="1" t="inlineStr"/>
       <c r="N484" s="1" t="inlineStr">
         <is>
-          <t>L1570: isolated marker/symbol line :: 4</t>
+          <t>L1388: isolated marker/symbol line :: c</t>
         </is>
       </c>
       <c r="O484" s="1" t="inlineStr"/>
@@ -18430,7 +18166,7 @@
       <c r="M485" s="1" t="inlineStr"/>
       <c r="N485" s="1" t="inlineStr">
         <is>
-          <t>L1573: isolated marker/symbol line :: B</t>
+          <t>L1401: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="O485" s="1" t="inlineStr"/>
@@ -18461,7 +18197,7 @@
       <c r="M486" s="1" t="inlineStr"/>
       <c r="N486" s="1" t="inlineStr">
         <is>
-          <t>L1579: isolated marker/symbol line :: 2</t>
+          <t>L1418: stray/suspicious non-ASCII glyph(s): U+4FDD CJK UNIFIED IDEOGRAPH-4FDD | isolated marker/symbol line :: 保</t>
         </is>
       </c>
       <c r="O486" s="1" t="inlineStr"/>
@@ -18492,7 +18228,7 @@
       <c r="M487" s="1" t="inlineStr"/>
       <c r="N487" s="1" t="inlineStr">
         <is>
-          <t>L1580: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | isolated marker/symbol line :: ç»´</t>
+          <t>L1419: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="O487" s="1" t="inlineStr"/>
@@ -18523,7 +18259,7 @@
       <c r="M488" s="1" t="inlineStr"/>
       <c r="N488" s="1" t="inlineStr">
         <is>
-          <t>L1611: isolated marker/symbol line :: T</t>
+          <t>L1427: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O488" s="1" t="inlineStr"/>
@@ -18554,7 +18290,7 @@
       <c r="M489" s="1" t="inlineStr"/>
       <c r="N489" s="1" t="inlineStr">
         <is>
-          <t>L1618: isolated marker/symbol line :: 5</t>
+          <t>L1428: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O489" s="1" t="inlineStr"/>
@@ -18585,7 +18321,7 @@
       <c r="M490" s="1" t="inlineStr"/>
       <c r="N490" s="1" t="inlineStr">
         <is>
-          <t>L1628: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1429: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O490" s="1" t="inlineStr"/>
@@ -18616,7 +18352,7 @@
       <c r="M491" s="1" t="inlineStr"/>
       <c r="N491" s="1" t="inlineStr">
         <is>
-          <t>L1630: isolated marker/symbol line :: 2</t>
+          <t>L1430: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O491" s="1" t="inlineStr"/>
@@ -18647,7 +18383,7 @@
       <c r="M492" s="1" t="inlineStr"/>
       <c r="N492" s="1" t="inlineStr">
         <is>
-          <t>L1633: isolated marker/symbol line :: 6</t>
+          <t>L1432: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O492" s="1" t="inlineStr"/>
@@ -18678,7 +18414,7 @@
       <c r="M493" s="1" t="inlineStr"/>
       <c r="N493" s="1" t="inlineStr">
         <is>
-          <t>L1635: isolated marker/symbol line :: 1</t>
+          <t>L1433: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O493" s="1" t="inlineStr"/>
@@ -18709,7 +18445,7 @@
       <c r="M494" s="1" t="inlineStr"/>
       <c r="N494" s="1" t="inlineStr">
         <is>
-          <t>L1636: isolated marker/symbol line :: 2</t>
+          <t>L1434: symbol-only separator/garbage line :: $2760.20</t>
         </is>
       </c>
       <c r="O494" s="1" t="inlineStr"/>
@@ -18740,7 +18476,7 @@
       <c r="M495" s="1" t="inlineStr"/>
       <c r="N495" s="1" t="inlineStr">
         <is>
-          <t>L1637: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1436: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O495" s="1" t="inlineStr"/>
@@ -18771,7 +18507,7 @@
       <c r="M496" s="1" t="inlineStr"/>
       <c r="N496" s="1" t="inlineStr">
         <is>
-          <t>L1639: isolated marker/symbol line :: ~</t>
+          <t>L1437: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O496" s="1" t="inlineStr"/>
@@ -18802,7 +18538,7 @@
       <c r="M497" s="1" t="inlineStr"/>
       <c r="N497" s="1" t="inlineStr">
         <is>
-          <t>L1640: isolated marker/symbol line :: 3</t>
+          <t>L1459: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O497" s="1" t="inlineStr"/>
@@ -18817,6 +18553,781 @@
       <c r="X497" s="1" t="inlineStr"/>
       <c r="Y497" s="1" t="inlineStr"/>
     </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr"/>
+      <c r="B498" s="1" t="inlineStr"/>
+      <c r="C498" s="1" t="inlineStr"/>
+      <c r="D498" s="1" t="inlineStr"/>
+      <c r="E498" s="1" t="inlineStr"/>
+      <c r="F498" s="1" t="inlineStr"/>
+      <c r="G498" s="1" t="inlineStr"/>
+      <c r="H498" s="1" t="inlineStr"/>
+      <c r="I498" s="1" t="inlineStr"/>
+      <c r="J498" s="1" t="inlineStr"/>
+      <c r="K498" s="1" t="inlineStr"/>
+      <c r="L498" s="1" t="inlineStr"/>
+      <c r="M498" s="1" t="inlineStr"/>
+      <c r="N498" s="1" t="inlineStr">
+        <is>
+          <t>L1467: isolated marker/symbol line :: i</t>
+        </is>
+      </c>
+      <c r="O498" s="1" t="inlineStr"/>
+      <c r="P498" s="1" t="inlineStr"/>
+      <c r="Q498" s="1" t="inlineStr"/>
+      <c r="R498" s="1" t="inlineStr"/>
+      <c r="S498" s="1" t="inlineStr"/>
+      <c r="T498" s="1" t="inlineStr"/>
+      <c r="U498" s="1" t="inlineStr"/>
+      <c r="V498" s="1" t="inlineStr"/>
+      <c r="W498" s="1" t="inlineStr"/>
+      <c r="X498" s="1" t="inlineStr"/>
+      <c r="Y498" s="1" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr"/>
+      <c r="B499" s="1" t="inlineStr"/>
+      <c r="C499" s="1" t="inlineStr"/>
+      <c r="D499" s="1" t="inlineStr"/>
+      <c r="E499" s="1" t="inlineStr"/>
+      <c r="F499" s="1" t="inlineStr"/>
+      <c r="G499" s="1" t="inlineStr"/>
+      <c r="H499" s="1" t="inlineStr"/>
+      <c r="I499" s="1" t="inlineStr"/>
+      <c r="J499" s="1" t="inlineStr"/>
+      <c r="K499" s="1" t="inlineStr"/>
+      <c r="L499" s="1" t="inlineStr"/>
+      <c r="M499" s="1" t="inlineStr"/>
+      <c r="N499" s="1" t="inlineStr">
+        <is>
+          <t>L1478: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="O499" s="1" t="inlineStr"/>
+      <c r="P499" s="1" t="inlineStr"/>
+      <c r="Q499" s="1" t="inlineStr"/>
+      <c r="R499" s="1" t="inlineStr"/>
+      <c r="S499" s="1" t="inlineStr"/>
+      <c r="T499" s="1" t="inlineStr"/>
+      <c r="U499" s="1" t="inlineStr"/>
+      <c r="V499" s="1" t="inlineStr"/>
+      <c r="W499" s="1" t="inlineStr"/>
+      <c r="X499" s="1" t="inlineStr"/>
+      <c r="Y499" s="1" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr"/>
+      <c r="B500" s="1" t="inlineStr"/>
+      <c r="C500" s="1" t="inlineStr"/>
+      <c r="D500" s="1" t="inlineStr"/>
+      <c r="E500" s="1" t="inlineStr"/>
+      <c r="F500" s="1" t="inlineStr"/>
+      <c r="G500" s="1" t="inlineStr"/>
+      <c r="H500" s="1" t="inlineStr"/>
+      <c r="I500" s="1" t="inlineStr"/>
+      <c r="J500" s="1" t="inlineStr"/>
+      <c r="K500" s="1" t="inlineStr"/>
+      <c r="L500" s="1" t="inlineStr"/>
+      <c r="M500" s="1" t="inlineStr"/>
+      <c r="N500" s="1" t="inlineStr">
+        <is>
+          <t>L1481: isolated marker/symbol line :: W $</t>
+        </is>
+      </c>
+      <c r="O500" s="1" t="inlineStr"/>
+      <c r="P500" s="1" t="inlineStr"/>
+      <c r="Q500" s="1" t="inlineStr"/>
+      <c r="R500" s="1" t="inlineStr"/>
+      <c r="S500" s="1" t="inlineStr"/>
+      <c r="T500" s="1" t="inlineStr"/>
+      <c r="U500" s="1" t="inlineStr"/>
+      <c r="V500" s="1" t="inlineStr"/>
+      <c r="W500" s="1" t="inlineStr"/>
+      <c r="X500" s="1" t="inlineStr"/>
+      <c r="Y500" s="1" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr"/>
+      <c r="B501" s="1" t="inlineStr"/>
+      <c r="C501" s="1" t="inlineStr"/>
+      <c r="D501" s="1" t="inlineStr"/>
+      <c r="E501" s="1" t="inlineStr"/>
+      <c r="F501" s="1" t="inlineStr"/>
+      <c r="G501" s="1" t="inlineStr"/>
+      <c r="H501" s="1" t="inlineStr"/>
+      <c r="I501" s="1" t="inlineStr"/>
+      <c r="J501" s="1" t="inlineStr"/>
+      <c r="K501" s="1" t="inlineStr"/>
+      <c r="L501" s="1" t="inlineStr"/>
+      <c r="M501" s="1" t="inlineStr"/>
+      <c r="N501" s="1" t="inlineStr">
+        <is>
+          <t>L1486: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O501" s="1" t="inlineStr"/>
+      <c r="P501" s="1" t="inlineStr"/>
+      <c r="Q501" s="1" t="inlineStr"/>
+      <c r="R501" s="1" t="inlineStr"/>
+      <c r="S501" s="1" t="inlineStr"/>
+      <c r="T501" s="1" t="inlineStr"/>
+      <c r="U501" s="1" t="inlineStr"/>
+      <c r="V501" s="1" t="inlineStr"/>
+      <c r="W501" s="1" t="inlineStr"/>
+      <c r="X501" s="1" t="inlineStr"/>
+      <c r="Y501" s="1" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr"/>
+      <c r="B502" s="1" t="inlineStr"/>
+      <c r="C502" s="1" t="inlineStr"/>
+      <c r="D502" s="1" t="inlineStr"/>
+      <c r="E502" s="1" t="inlineStr"/>
+      <c r="F502" s="1" t="inlineStr"/>
+      <c r="G502" s="1" t="inlineStr"/>
+      <c r="H502" s="1" t="inlineStr"/>
+      <c r="I502" s="1" t="inlineStr"/>
+      <c r="J502" s="1" t="inlineStr"/>
+      <c r="K502" s="1" t="inlineStr"/>
+      <c r="L502" s="1" t="inlineStr"/>
+      <c r="M502" s="1" t="inlineStr"/>
+      <c r="N502" s="1" t="inlineStr">
+        <is>
+          <t>L1524: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O502" s="1" t="inlineStr"/>
+      <c r="P502" s="1" t="inlineStr"/>
+      <c r="Q502" s="1" t="inlineStr"/>
+      <c r="R502" s="1" t="inlineStr"/>
+      <c r="S502" s="1" t="inlineStr"/>
+      <c r="T502" s="1" t="inlineStr"/>
+      <c r="U502" s="1" t="inlineStr"/>
+      <c r="V502" s="1" t="inlineStr"/>
+      <c r="W502" s="1" t="inlineStr"/>
+      <c r="X502" s="1" t="inlineStr"/>
+      <c r="Y502" s="1" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr"/>
+      <c r="B503" s="1" t="inlineStr"/>
+      <c r="C503" s="1" t="inlineStr"/>
+      <c r="D503" s="1" t="inlineStr"/>
+      <c r="E503" s="1" t="inlineStr"/>
+      <c r="F503" s="1" t="inlineStr"/>
+      <c r="G503" s="1" t="inlineStr"/>
+      <c r="H503" s="1" t="inlineStr"/>
+      <c r="I503" s="1" t="inlineStr"/>
+      <c r="J503" s="1" t="inlineStr"/>
+      <c r="K503" s="1" t="inlineStr"/>
+      <c r="L503" s="1" t="inlineStr"/>
+      <c r="M503" s="1" t="inlineStr"/>
+      <c r="N503" s="1" t="inlineStr">
+        <is>
+          <t>L1529: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="O503" s="1" t="inlineStr"/>
+      <c r="P503" s="1" t="inlineStr"/>
+      <c r="Q503" s="1" t="inlineStr"/>
+      <c r="R503" s="1" t="inlineStr"/>
+      <c r="S503" s="1" t="inlineStr"/>
+      <c r="T503" s="1" t="inlineStr"/>
+      <c r="U503" s="1" t="inlineStr"/>
+      <c r="V503" s="1" t="inlineStr"/>
+      <c r="W503" s="1" t="inlineStr"/>
+      <c r="X503" s="1" t="inlineStr"/>
+      <c r="Y503" s="1" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr"/>
+      <c r="B504" s="1" t="inlineStr"/>
+      <c r="C504" s="1" t="inlineStr"/>
+      <c r="D504" s="1" t="inlineStr"/>
+      <c r="E504" s="1" t="inlineStr"/>
+      <c r="F504" s="1" t="inlineStr"/>
+      <c r="G504" s="1" t="inlineStr"/>
+      <c r="H504" s="1" t="inlineStr"/>
+      <c r="I504" s="1" t="inlineStr"/>
+      <c r="J504" s="1" t="inlineStr"/>
+      <c r="K504" s="1" t="inlineStr"/>
+      <c r="L504" s="1" t="inlineStr"/>
+      <c r="M504" s="1" t="inlineStr"/>
+      <c r="N504" s="1" t="inlineStr">
+        <is>
+          <t>L1531: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O504" s="1" t="inlineStr"/>
+      <c r="P504" s="1" t="inlineStr"/>
+      <c r="Q504" s="1" t="inlineStr"/>
+      <c r="R504" s="1" t="inlineStr"/>
+      <c r="S504" s="1" t="inlineStr"/>
+      <c r="T504" s="1" t="inlineStr"/>
+      <c r="U504" s="1" t="inlineStr"/>
+      <c r="V504" s="1" t="inlineStr"/>
+      <c r="W504" s="1" t="inlineStr"/>
+      <c r="X504" s="1" t="inlineStr"/>
+      <c r="Y504" s="1" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr"/>
+      <c r="B505" s="1" t="inlineStr"/>
+      <c r="C505" s="1" t="inlineStr"/>
+      <c r="D505" s="1" t="inlineStr"/>
+      <c r="E505" s="1" t="inlineStr"/>
+      <c r="F505" s="1" t="inlineStr"/>
+      <c r="G505" s="1" t="inlineStr"/>
+      <c r="H505" s="1" t="inlineStr"/>
+      <c r="I505" s="1" t="inlineStr"/>
+      <c r="J505" s="1" t="inlineStr"/>
+      <c r="K505" s="1" t="inlineStr"/>
+      <c r="L505" s="1" t="inlineStr"/>
+      <c r="M505" s="1" t="inlineStr"/>
+      <c r="N505" s="1" t="inlineStr">
+        <is>
+          <t>L1561: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O505" s="1" t="inlineStr"/>
+      <c r="P505" s="1" t="inlineStr"/>
+      <c r="Q505" s="1" t="inlineStr"/>
+      <c r="R505" s="1" t="inlineStr"/>
+      <c r="S505" s="1" t="inlineStr"/>
+      <c r="T505" s="1" t="inlineStr"/>
+      <c r="U505" s="1" t="inlineStr"/>
+      <c r="V505" s="1" t="inlineStr"/>
+      <c r="W505" s="1" t="inlineStr"/>
+      <c r="X505" s="1" t="inlineStr"/>
+      <c r="Y505" s="1" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr"/>
+      <c r="B506" s="1" t="inlineStr"/>
+      <c r="C506" s="1" t="inlineStr"/>
+      <c r="D506" s="1" t="inlineStr"/>
+      <c r="E506" s="1" t="inlineStr"/>
+      <c r="F506" s="1" t="inlineStr"/>
+      <c r="G506" s="1" t="inlineStr"/>
+      <c r="H506" s="1" t="inlineStr"/>
+      <c r="I506" s="1" t="inlineStr"/>
+      <c r="J506" s="1" t="inlineStr"/>
+      <c r="K506" s="1" t="inlineStr"/>
+      <c r="L506" s="1" t="inlineStr"/>
+      <c r="M506" s="1" t="inlineStr"/>
+      <c r="N506" s="1" t="inlineStr">
+        <is>
+          <t>L1569: stray/suspicious non-ASCII glyph(s): U+94F6 CJK UNIFIED IDEOGRAPH-94F6 | isolated marker/symbol line :: 银</t>
+        </is>
+      </c>
+      <c r="O506" s="1" t="inlineStr"/>
+      <c r="P506" s="1" t="inlineStr"/>
+      <c r="Q506" s="1" t="inlineStr"/>
+      <c r="R506" s="1" t="inlineStr"/>
+      <c r="S506" s="1" t="inlineStr"/>
+      <c r="T506" s="1" t="inlineStr"/>
+      <c r="U506" s="1" t="inlineStr"/>
+      <c r="V506" s="1" t="inlineStr"/>
+      <c r="W506" s="1" t="inlineStr"/>
+      <c r="X506" s="1" t="inlineStr"/>
+      <c r="Y506" s="1" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr"/>
+      <c r="B507" s="1" t="inlineStr"/>
+      <c r="C507" s="1" t="inlineStr"/>
+      <c r="D507" s="1" t="inlineStr"/>
+      <c r="E507" s="1" t="inlineStr"/>
+      <c r="F507" s="1" t="inlineStr"/>
+      <c r="G507" s="1" t="inlineStr"/>
+      <c r="H507" s="1" t="inlineStr"/>
+      <c r="I507" s="1" t="inlineStr"/>
+      <c r="J507" s="1" t="inlineStr"/>
+      <c r="K507" s="1" t="inlineStr"/>
+      <c r="L507" s="1" t="inlineStr"/>
+      <c r="M507" s="1" t="inlineStr"/>
+      <c r="N507" s="1" t="inlineStr">
+        <is>
+          <t>L1570: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O507" s="1" t="inlineStr"/>
+      <c r="P507" s="1" t="inlineStr"/>
+      <c r="Q507" s="1" t="inlineStr"/>
+      <c r="R507" s="1" t="inlineStr"/>
+      <c r="S507" s="1" t="inlineStr"/>
+      <c r="T507" s="1" t="inlineStr"/>
+      <c r="U507" s="1" t="inlineStr"/>
+      <c r="V507" s="1" t="inlineStr"/>
+      <c r="W507" s="1" t="inlineStr"/>
+      <c r="X507" s="1" t="inlineStr"/>
+      <c r="Y507" s="1" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr"/>
+      <c r="B508" s="1" t="inlineStr"/>
+      <c r="C508" s="1" t="inlineStr"/>
+      <c r="D508" s="1" t="inlineStr"/>
+      <c r="E508" s="1" t="inlineStr"/>
+      <c r="F508" s="1" t="inlineStr"/>
+      <c r="G508" s="1" t="inlineStr"/>
+      <c r="H508" s="1" t="inlineStr"/>
+      <c r="I508" s="1" t="inlineStr"/>
+      <c r="J508" s="1" t="inlineStr"/>
+      <c r="K508" s="1" t="inlineStr"/>
+      <c r="L508" s="1" t="inlineStr"/>
+      <c r="M508" s="1" t="inlineStr"/>
+      <c r="N508" s="1" t="inlineStr">
+        <is>
+          <t>L1573: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
+      <c r="O508" s="1" t="inlineStr"/>
+      <c r="P508" s="1" t="inlineStr"/>
+      <c r="Q508" s="1" t="inlineStr"/>
+      <c r="R508" s="1" t="inlineStr"/>
+      <c r="S508" s="1" t="inlineStr"/>
+      <c r="T508" s="1" t="inlineStr"/>
+      <c r="U508" s="1" t="inlineStr"/>
+      <c r="V508" s="1" t="inlineStr"/>
+      <c r="W508" s="1" t="inlineStr"/>
+      <c r="X508" s="1" t="inlineStr"/>
+      <c r="Y508" s="1" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr"/>
+      <c r="B509" s="1" t="inlineStr"/>
+      <c r="C509" s="1" t="inlineStr"/>
+      <c r="D509" s="1" t="inlineStr"/>
+      <c r="E509" s="1" t="inlineStr"/>
+      <c r="F509" s="1" t="inlineStr"/>
+      <c r="G509" s="1" t="inlineStr"/>
+      <c r="H509" s="1" t="inlineStr"/>
+      <c r="I509" s="1" t="inlineStr"/>
+      <c r="J509" s="1" t="inlineStr"/>
+      <c r="K509" s="1" t="inlineStr"/>
+      <c r="L509" s="1" t="inlineStr"/>
+      <c r="M509" s="1" t="inlineStr"/>
+      <c r="N509" s="1" t="inlineStr">
+        <is>
+          <t>L1579: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O509" s="1" t="inlineStr"/>
+      <c r="P509" s="1" t="inlineStr"/>
+      <c r="Q509" s="1" t="inlineStr"/>
+      <c r="R509" s="1" t="inlineStr"/>
+      <c r="S509" s="1" t="inlineStr"/>
+      <c r="T509" s="1" t="inlineStr"/>
+      <c r="U509" s="1" t="inlineStr"/>
+      <c r="V509" s="1" t="inlineStr"/>
+      <c r="W509" s="1" t="inlineStr"/>
+      <c r="X509" s="1" t="inlineStr"/>
+      <c r="Y509" s="1" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr"/>
+      <c r="B510" s="1" t="inlineStr"/>
+      <c r="C510" s="1" t="inlineStr"/>
+      <c r="D510" s="1" t="inlineStr"/>
+      <c r="E510" s="1" t="inlineStr"/>
+      <c r="F510" s="1" t="inlineStr"/>
+      <c r="G510" s="1" t="inlineStr"/>
+      <c r="H510" s="1" t="inlineStr"/>
+      <c r="I510" s="1" t="inlineStr"/>
+      <c r="J510" s="1" t="inlineStr"/>
+      <c r="K510" s="1" t="inlineStr"/>
+      <c r="L510" s="1" t="inlineStr"/>
+      <c r="M510" s="1" t="inlineStr"/>
+      <c r="N510" s="1" t="inlineStr">
+        <is>
+          <t>L1580: stray/suspicious non-ASCII glyph(s): U+7EF4 CJK UNIFIED IDEOGRAPH-7EF4 | isolated marker/symbol line :: 维</t>
+        </is>
+      </c>
+      <c r="O510" s="1" t="inlineStr"/>
+      <c r="P510" s="1" t="inlineStr"/>
+      <c r="Q510" s="1" t="inlineStr"/>
+      <c r="R510" s="1" t="inlineStr"/>
+      <c r="S510" s="1" t="inlineStr"/>
+      <c r="T510" s="1" t="inlineStr"/>
+      <c r="U510" s="1" t="inlineStr"/>
+      <c r="V510" s="1" t="inlineStr"/>
+      <c r="W510" s="1" t="inlineStr"/>
+      <c r="X510" s="1" t="inlineStr"/>
+      <c r="Y510" s="1" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr"/>
+      <c r="B511" s="1" t="inlineStr"/>
+      <c r="C511" s="1" t="inlineStr"/>
+      <c r="D511" s="1" t="inlineStr"/>
+      <c r="E511" s="1" t="inlineStr"/>
+      <c r="F511" s="1" t="inlineStr"/>
+      <c r="G511" s="1" t="inlineStr"/>
+      <c r="H511" s="1" t="inlineStr"/>
+      <c r="I511" s="1" t="inlineStr"/>
+      <c r="J511" s="1" t="inlineStr"/>
+      <c r="K511" s="1" t="inlineStr"/>
+      <c r="L511" s="1" t="inlineStr"/>
+      <c r="M511" s="1" t="inlineStr"/>
+      <c r="N511" s="1" t="inlineStr">
+        <is>
+          <t>L1611: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
+      <c r="O511" s="1" t="inlineStr"/>
+      <c r="P511" s="1" t="inlineStr"/>
+      <c r="Q511" s="1" t="inlineStr"/>
+      <c r="R511" s="1" t="inlineStr"/>
+      <c r="S511" s="1" t="inlineStr"/>
+      <c r="T511" s="1" t="inlineStr"/>
+      <c r="U511" s="1" t="inlineStr"/>
+      <c r="V511" s="1" t="inlineStr"/>
+      <c r="W511" s="1" t="inlineStr"/>
+      <c r="X511" s="1" t="inlineStr"/>
+      <c r="Y511" s="1" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr"/>
+      <c r="B512" s="1" t="inlineStr"/>
+      <c r="C512" s="1" t="inlineStr"/>
+      <c r="D512" s="1" t="inlineStr"/>
+      <c r="E512" s="1" t="inlineStr"/>
+      <c r="F512" s="1" t="inlineStr"/>
+      <c r="G512" s="1" t="inlineStr"/>
+      <c r="H512" s="1" t="inlineStr"/>
+      <c r="I512" s="1" t="inlineStr"/>
+      <c r="J512" s="1" t="inlineStr"/>
+      <c r="K512" s="1" t="inlineStr"/>
+      <c r="L512" s="1" t="inlineStr"/>
+      <c r="M512" s="1" t="inlineStr"/>
+      <c r="N512" s="1" t="inlineStr">
+        <is>
+          <t>L1618: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O512" s="1" t="inlineStr"/>
+      <c r="P512" s="1" t="inlineStr"/>
+      <c r="Q512" s="1" t="inlineStr"/>
+      <c r="R512" s="1" t="inlineStr"/>
+      <c r="S512" s="1" t="inlineStr"/>
+      <c r="T512" s="1" t="inlineStr"/>
+      <c r="U512" s="1" t="inlineStr"/>
+      <c r="V512" s="1" t="inlineStr"/>
+      <c r="W512" s="1" t="inlineStr"/>
+      <c r="X512" s="1" t="inlineStr"/>
+      <c r="Y512" s="1" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr"/>
+      <c r="B513" s="1" t="inlineStr"/>
+      <c r="C513" s="1" t="inlineStr"/>
+      <c r="D513" s="1" t="inlineStr"/>
+      <c r="E513" s="1" t="inlineStr"/>
+      <c r="F513" s="1" t="inlineStr"/>
+      <c r="G513" s="1" t="inlineStr"/>
+      <c r="H513" s="1" t="inlineStr"/>
+      <c r="I513" s="1" t="inlineStr"/>
+      <c r="J513" s="1" t="inlineStr"/>
+      <c r="K513" s="1" t="inlineStr"/>
+      <c r="L513" s="1" t="inlineStr"/>
+      <c r="M513" s="1" t="inlineStr"/>
+      <c r="N513" s="1" t="inlineStr">
+        <is>
+          <t>L1628: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O513" s="1" t="inlineStr"/>
+      <c r="P513" s="1" t="inlineStr"/>
+      <c r="Q513" s="1" t="inlineStr"/>
+      <c r="R513" s="1" t="inlineStr"/>
+      <c r="S513" s="1" t="inlineStr"/>
+      <c r="T513" s="1" t="inlineStr"/>
+      <c r="U513" s="1" t="inlineStr"/>
+      <c r="V513" s="1" t="inlineStr"/>
+      <c r="W513" s="1" t="inlineStr"/>
+      <c r="X513" s="1" t="inlineStr"/>
+      <c r="Y513" s="1" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr"/>
+      <c r="B514" s="1" t="inlineStr"/>
+      <c r="C514" s="1" t="inlineStr"/>
+      <c r="D514" s="1" t="inlineStr"/>
+      <c r="E514" s="1" t="inlineStr"/>
+      <c r="F514" s="1" t="inlineStr"/>
+      <c r="G514" s="1" t="inlineStr"/>
+      <c r="H514" s="1" t="inlineStr"/>
+      <c r="I514" s="1" t="inlineStr"/>
+      <c r="J514" s="1" t="inlineStr"/>
+      <c r="K514" s="1" t="inlineStr"/>
+      <c r="L514" s="1" t="inlineStr"/>
+      <c r="M514" s="1" t="inlineStr"/>
+      <c r="N514" s="1" t="inlineStr">
+        <is>
+          <t>L1630: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O514" s="1" t="inlineStr"/>
+      <c r="P514" s="1" t="inlineStr"/>
+      <c r="Q514" s="1" t="inlineStr"/>
+      <c r="R514" s="1" t="inlineStr"/>
+      <c r="S514" s="1" t="inlineStr"/>
+      <c r="T514" s="1" t="inlineStr"/>
+      <c r="U514" s="1" t="inlineStr"/>
+      <c r="V514" s="1" t="inlineStr"/>
+      <c r="W514" s="1" t="inlineStr"/>
+      <c r="X514" s="1" t="inlineStr"/>
+      <c r="Y514" s="1" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr"/>
+      <c r="B515" s="1" t="inlineStr"/>
+      <c r="C515" s="1" t="inlineStr"/>
+      <c r="D515" s="1" t="inlineStr"/>
+      <c r="E515" s="1" t="inlineStr"/>
+      <c r="F515" s="1" t="inlineStr"/>
+      <c r="G515" s="1" t="inlineStr"/>
+      <c r="H515" s="1" t="inlineStr"/>
+      <c r="I515" s="1" t="inlineStr"/>
+      <c r="J515" s="1" t="inlineStr"/>
+      <c r="K515" s="1" t="inlineStr"/>
+      <c r="L515" s="1" t="inlineStr"/>
+      <c r="M515" s="1" t="inlineStr"/>
+      <c r="N515" s="1" t="inlineStr">
+        <is>
+          <t>L1631: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
+        </is>
+      </c>
+      <c r="O515" s="1" t="inlineStr"/>
+      <c r="P515" s="1" t="inlineStr"/>
+      <c r="Q515" s="1" t="inlineStr"/>
+      <c r="R515" s="1" t="inlineStr"/>
+      <c r="S515" s="1" t="inlineStr"/>
+      <c r="T515" s="1" t="inlineStr"/>
+      <c r="U515" s="1" t="inlineStr"/>
+      <c r="V515" s="1" t="inlineStr"/>
+      <c r="W515" s="1" t="inlineStr"/>
+      <c r="X515" s="1" t="inlineStr"/>
+      <c r="Y515" s="1" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr"/>
+      <c r="B516" s="1" t="inlineStr"/>
+      <c r="C516" s="1" t="inlineStr"/>
+      <c r="D516" s="1" t="inlineStr"/>
+      <c r="E516" s="1" t="inlineStr"/>
+      <c r="F516" s="1" t="inlineStr"/>
+      <c r="G516" s="1" t="inlineStr"/>
+      <c r="H516" s="1" t="inlineStr"/>
+      <c r="I516" s="1" t="inlineStr"/>
+      <c r="J516" s="1" t="inlineStr"/>
+      <c r="K516" s="1" t="inlineStr"/>
+      <c r="L516" s="1" t="inlineStr"/>
+      <c r="M516" s="1" t="inlineStr"/>
+      <c r="N516" s="1" t="inlineStr">
+        <is>
+          <t>L1633: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O516" s="1" t="inlineStr"/>
+      <c r="P516" s="1" t="inlineStr"/>
+      <c r="Q516" s="1" t="inlineStr"/>
+      <c r="R516" s="1" t="inlineStr"/>
+      <c r="S516" s="1" t="inlineStr"/>
+      <c r="T516" s="1" t="inlineStr"/>
+      <c r="U516" s="1" t="inlineStr"/>
+      <c r="V516" s="1" t="inlineStr"/>
+      <c r="W516" s="1" t="inlineStr"/>
+      <c r="X516" s="1" t="inlineStr"/>
+      <c r="Y516" s="1" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr"/>
+      <c r="B517" s="1" t="inlineStr"/>
+      <c r="C517" s="1" t="inlineStr"/>
+      <c r="D517" s="1" t="inlineStr"/>
+      <c r="E517" s="1" t="inlineStr"/>
+      <c r="F517" s="1" t="inlineStr"/>
+      <c r="G517" s="1" t="inlineStr"/>
+      <c r="H517" s="1" t="inlineStr"/>
+      <c r="I517" s="1" t="inlineStr"/>
+      <c r="J517" s="1" t="inlineStr"/>
+      <c r="K517" s="1" t="inlineStr"/>
+      <c r="L517" s="1" t="inlineStr"/>
+      <c r="M517" s="1" t="inlineStr"/>
+      <c r="N517" s="1" t="inlineStr">
+        <is>
+          <t>L1635: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O517" s="1" t="inlineStr"/>
+      <c r="P517" s="1" t="inlineStr"/>
+      <c r="Q517" s="1" t="inlineStr"/>
+      <c r="R517" s="1" t="inlineStr"/>
+      <c r="S517" s="1" t="inlineStr"/>
+      <c r="T517" s="1" t="inlineStr"/>
+      <c r="U517" s="1" t="inlineStr"/>
+      <c r="V517" s="1" t="inlineStr"/>
+      <c r="W517" s="1" t="inlineStr"/>
+      <c r="X517" s="1" t="inlineStr"/>
+      <c r="Y517" s="1" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr"/>
+      <c r="B518" s="1" t="inlineStr"/>
+      <c r="C518" s="1" t="inlineStr"/>
+      <c r="D518" s="1" t="inlineStr"/>
+      <c r="E518" s="1" t="inlineStr"/>
+      <c r="F518" s="1" t="inlineStr"/>
+      <c r="G518" s="1" t="inlineStr"/>
+      <c r="H518" s="1" t="inlineStr"/>
+      <c r="I518" s="1" t="inlineStr"/>
+      <c r="J518" s="1" t="inlineStr"/>
+      <c r="K518" s="1" t="inlineStr"/>
+      <c r="L518" s="1" t="inlineStr"/>
+      <c r="M518" s="1" t="inlineStr"/>
+      <c r="N518" s="1" t="inlineStr">
+        <is>
+          <t>L1636: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O518" s="1" t="inlineStr"/>
+      <c r="P518" s="1" t="inlineStr"/>
+      <c r="Q518" s="1" t="inlineStr"/>
+      <c r="R518" s="1" t="inlineStr"/>
+      <c r="S518" s="1" t="inlineStr"/>
+      <c r="T518" s="1" t="inlineStr"/>
+      <c r="U518" s="1" t="inlineStr"/>
+      <c r="V518" s="1" t="inlineStr"/>
+      <c r="W518" s="1" t="inlineStr"/>
+      <c r="X518" s="1" t="inlineStr"/>
+      <c r="Y518" s="1" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr"/>
+      <c r="B519" s="1" t="inlineStr"/>
+      <c r="C519" s="1" t="inlineStr"/>
+      <c r="D519" s="1" t="inlineStr"/>
+      <c r="E519" s="1" t="inlineStr"/>
+      <c r="F519" s="1" t="inlineStr"/>
+      <c r="G519" s="1" t="inlineStr"/>
+      <c r="H519" s="1" t="inlineStr"/>
+      <c r="I519" s="1" t="inlineStr"/>
+      <c r="J519" s="1" t="inlineStr"/>
+      <c r="K519" s="1" t="inlineStr"/>
+      <c r="L519" s="1" t="inlineStr"/>
+      <c r="M519" s="1" t="inlineStr"/>
+      <c r="N519" s="1" t="inlineStr">
+        <is>
+          <t>L1637: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O519" s="1" t="inlineStr"/>
+      <c r="P519" s="1" t="inlineStr"/>
+      <c r="Q519" s="1" t="inlineStr"/>
+      <c r="R519" s="1" t="inlineStr"/>
+      <c r="S519" s="1" t="inlineStr"/>
+      <c r="T519" s="1" t="inlineStr"/>
+      <c r="U519" s="1" t="inlineStr"/>
+      <c r="V519" s="1" t="inlineStr"/>
+      <c r="W519" s="1" t="inlineStr"/>
+      <c r="X519" s="1" t="inlineStr"/>
+      <c r="Y519" s="1" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr"/>
+      <c r="B520" s="1" t="inlineStr"/>
+      <c r="C520" s="1" t="inlineStr"/>
+      <c r="D520" s="1" t="inlineStr"/>
+      <c r="E520" s="1" t="inlineStr"/>
+      <c r="F520" s="1" t="inlineStr"/>
+      <c r="G520" s="1" t="inlineStr"/>
+      <c r="H520" s="1" t="inlineStr"/>
+      <c r="I520" s="1" t="inlineStr"/>
+      <c r="J520" s="1" t="inlineStr"/>
+      <c r="K520" s="1" t="inlineStr"/>
+      <c r="L520" s="1" t="inlineStr"/>
+      <c r="M520" s="1" t="inlineStr"/>
+      <c r="N520" s="1" t="inlineStr">
+        <is>
+          <t>L1638: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: 2 ，</t>
+        </is>
+      </c>
+      <c r="O520" s="1" t="inlineStr"/>
+      <c r="P520" s="1" t="inlineStr"/>
+      <c r="Q520" s="1" t="inlineStr"/>
+      <c r="R520" s="1" t="inlineStr"/>
+      <c r="S520" s="1" t="inlineStr"/>
+      <c r="T520" s="1" t="inlineStr"/>
+      <c r="U520" s="1" t="inlineStr"/>
+      <c r="V520" s="1" t="inlineStr"/>
+      <c r="W520" s="1" t="inlineStr"/>
+      <c r="X520" s="1" t="inlineStr"/>
+      <c r="Y520" s="1" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr"/>
+      <c r="B521" s="1" t="inlineStr"/>
+      <c r="C521" s="1" t="inlineStr"/>
+      <c r="D521" s="1" t="inlineStr"/>
+      <c r="E521" s="1" t="inlineStr"/>
+      <c r="F521" s="1" t="inlineStr"/>
+      <c r="G521" s="1" t="inlineStr"/>
+      <c r="H521" s="1" t="inlineStr"/>
+      <c r="I521" s="1" t="inlineStr"/>
+      <c r="J521" s="1" t="inlineStr"/>
+      <c r="K521" s="1" t="inlineStr"/>
+      <c r="L521" s="1" t="inlineStr"/>
+      <c r="M521" s="1" t="inlineStr"/>
+      <c r="N521" s="1" t="inlineStr">
+        <is>
+          <t>L1639: isolated marker/symbol line :: ~</t>
+        </is>
+      </c>
+      <c r="O521" s="1" t="inlineStr"/>
+      <c r="P521" s="1" t="inlineStr"/>
+      <c r="Q521" s="1" t="inlineStr"/>
+      <c r="R521" s="1" t="inlineStr"/>
+      <c r="S521" s="1" t="inlineStr"/>
+      <c r="T521" s="1" t="inlineStr"/>
+      <c r="U521" s="1" t="inlineStr"/>
+      <c r="V521" s="1" t="inlineStr"/>
+      <c r="W521" s="1" t="inlineStr"/>
+      <c r="X521" s="1" t="inlineStr"/>
+      <c r="Y521" s="1" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr"/>
+      <c r="B522" s="1" t="inlineStr"/>
+      <c r="C522" s="1" t="inlineStr"/>
+      <c r="D522" s="1" t="inlineStr"/>
+      <c r="E522" s="1" t="inlineStr"/>
+      <c r="F522" s="1" t="inlineStr"/>
+      <c r="G522" s="1" t="inlineStr"/>
+      <c r="H522" s="1" t="inlineStr"/>
+      <c r="I522" s="1" t="inlineStr"/>
+      <c r="J522" s="1" t="inlineStr"/>
+      <c r="K522" s="1" t="inlineStr"/>
+      <c r="L522" s="1" t="inlineStr"/>
+      <c r="M522" s="1" t="inlineStr"/>
+      <c r="N522" s="1" t="inlineStr">
+        <is>
+          <t>L1640: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O522" s="1" t="inlineStr"/>
+      <c r="P522" s="1" t="inlineStr"/>
+      <c r="Q522" s="1" t="inlineStr"/>
+      <c r="R522" s="1" t="inlineStr"/>
+      <c r="S522" s="1" t="inlineStr"/>
+      <c r="T522" s="1" t="inlineStr"/>
+      <c r="U522" s="1" t="inlineStr"/>
+      <c r="V522" s="1" t="inlineStr"/>
+      <c r="W522" s="1" t="inlineStr"/>
+      <c r="X522" s="1" t="inlineStr"/>
+      <c r="Y522" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
